--- a/test_cases/disturbance_profile_15.xlsx
+++ b/test_cases/disturbance_profile_15.xlsx
@@ -418,7 +418,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -429,7 +429,7 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="B3">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -440,7 +440,7 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="B4">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -451,7 +451,7 @@
         <v>0.1</v>
       </c>
       <c r="B5">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -462,7 +462,7 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="B6">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -473,7 +473,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="B7">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -484,7 +484,7 @@
         <v>0.2</v>
       </c>
       <c r="B8">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -495,7 +495,7 @@
         <v>0.2333333333333333</v>
       </c>
       <c r="B9">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -506,7 +506,7 @@
         <v>0.2666666666666667</v>
       </c>
       <c r="B10">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -517,7 +517,7 @@
         <v>0.3</v>
       </c>
       <c r="B11">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="B12">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -539,7 +539,7 @@
         <v>0.3666666666666666</v>
       </c>
       <c r="B13">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>0.4</v>
       </c>
       <c r="B14">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>0.4333333333333333</v>
       </c>
       <c r="B15">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>0.4666666666666666</v>
       </c>
       <c r="B16">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -583,7 +583,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="B17">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -594,7 +594,7 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="B18">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -605,7 +605,7 @@
         <v>0.5666666666666667</v>
       </c>
       <c r="B19">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -616,7 +616,7 @@
         <v>0.6</v>
       </c>
       <c r="B20">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -627,7 +627,7 @@
         <v>0.6333333333333333</v>
       </c>
       <c r="B21">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -638,7 +638,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="B22">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -649,7 +649,7 @@
         <v>0.7</v>
       </c>
       <c r="B23">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>0.7333333333333333</v>
       </c>
       <c r="B24">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -671,7 +671,7 @@
         <v>0.7666666666666666</v>
       </c>
       <c r="B25">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -682,7 +682,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="B26">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -693,7 +693,7 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="B27">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>0.8666666666666666</v>
       </c>
       <c r="B28">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -715,7 +715,7 @@
         <v>0.8999999999999999</v>
       </c>
       <c r="B29">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>0.9333333333333332</v>
       </c>
       <c r="B30">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -737,7 +737,7 @@
         <v>0.9666666666666666</v>
       </c>
       <c r="B31">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>0.9999</v>
       </c>
       <c r="B32">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -759,7 +759,7 @@
         <v>1</v>
       </c>
       <c r="B33">
-        <v>0.9948010059065188</v>
+        <v>0.9999999997385224</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -770,10 +770,10 @@
         <v>1.0001</v>
       </c>
       <c r="B34">
-        <v>0.9399525547968174</v>
+        <v>0.9857203003919214</v>
       </c>
       <c r="C34">
-        <v>0.9999480333499405</v>
+        <v>0.9999968871430416</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -781,10 +781,10 @@
         <v>1.033433333333333</v>
       </c>
       <c r="B35">
-        <v>0.942962614548697</v>
+        <v>0.9857005306355356</v>
       </c>
       <c r="C35">
-        <v>0.988835959598549</v>
+        <v>0.9990034065750755</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -792,10 +792,10 @@
         <v>1.066766666666667</v>
       </c>
       <c r="B36">
-        <v>0.9408920943885954</v>
+        <v>0.985641722043312</v>
       </c>
       <c r="C36">
-        <v>0.996555903958285</v>
+        <v>0.9991034860621262</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -803,10 +803,10 @@
         <v>1.1001</v>
       </c>
       <c r="B37">
-        <v>0.9369808332999515</v>
+        <v>0.985545127246805</v>
       </c>
       <c r="C37">
-        <v>0.9980704648661848</v>
+        <v>0.9991549746101226</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -814,10 +814,10 @@
         <v>1.133433333333334</v>
       </c>
       <c r="B38">
-        <v>0.9311041251347852</v>
+        <v>0.9854133465905087</v>
       </c>
       <c r="C38">
-        <v>0.9979402958008655</v>
+        <v>0.9990970419507069</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -825,10 +825,10 @@
         <v>1.166766666666667</v>
       </c>
       <c r="B39">
-        <v>0.9236342935696455</v>
+        <v>0.9852510343769917</v>
       </c>
       <c r="C39">
-        <v>0.9977526153092634</v>
+        <v>0.9989549155718888</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -836,10 +836,10 @@
         <v>1.200100000000001</v>
       </c>
       <c r="B40">
-        <v>0.9153451832819154</v>
+        <v>0.9850653811077105</v>
       </c>
       <c r="C40">
-        <v>0.9977534081580864</v>
+        <v>0.9987528999256444</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>1.233433333333334</v>
       </c>
       <c r="B41">
-        <v>0.9072727102184752</v>
+        <v>0.9848661310183278</v>
       </c>
       <c r="C41">
-        <v>0.9979551001188354</v>
+        <v>0.9985089600774482</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -858,10 +858,10 @@
         <v>1.266766666666667</v>
       </c>
       <c r="B42">
-        <v>0.9004757556518121</v>
+        <v>0.9846650530543511</v>
       </c>
       <c r="C42">
-        <v>0.9983241039310454</v>
+        <v>0.99823600009494</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -869,10 +869,10 @@
         <v>1.300100000000001</v>
       </c>
       <c r="B43">
-        <v>0.895812581834773</v>
+        <v>0.9844749675273811</v>
       </c>
       <c r="C43">
-        <v>0.9988134941481522</v>
+        <v>0.9979432370411006</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -880,10 +880,10 @@
         <v>1.333433333333334</v>
       </c>
       <c r="B44">
-        <v>0.8937826143944468</v>
+        <v>0.9843085585799927</v>
       </c>
       <c r="C44">
-        <v>0.9993732134775398</v>
+        <v>0.9976372216239016</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -891,10 +891,10 @@
         <v>1.366766666666668</v>
       </c>
       <c r="B45">
-        <v>0.8944624157283537</v>
+        <v>0.9841772332453784</v>
       </c>
       <c r="C45">
-        <v>0.9999544952269346</v>
+        <v>0.9973225736447232</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -902,10 +902,10 @@
         <v>1.400100000000001</v>
       </c>
       <c r="B46">
-        <v>0.8975334954505275</v>
+        <v>0.9840902215303189</v>
       </c>
       <c r="C46">
-        <v>1.000511712791733</v>
+        <v>0.9970025165149983</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -913,10 +913,10 @@
         <v>1.433433333333335</v>
       </c>
       <c r="B47">
-        <v>0.9023852465769078</v>
+        <v>0.984053990795532</v>
       </c>
       <c r="C47">
-        <v>1.001003476121455</v>
+        <v>0.9966792693731393</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -924,10 +924,10 @@
         <v>1.466766666666668</v>
       </c>
       <c r="B48">
-        <v>0.9082629349428158</v>
+        <v>0.9840719320327371</v>
       </c>
       <c r="C48">
-        <v>1.001394243069338</v>
+        <v>0.99635434049587</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -935,10 +935,10 @@
         <v>1.500100000000002</v>
       </c>
       <c r="B49">
-        <v>0.9144237735329865</v>
+        <v>0.9841442149971967</v>
       </c>
       <c r="C49">
-        <v>1.001656425561309</v>
+        <v>0.9960287440915827</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -946,10 +946,10 @@
         <v>1.533433333333335</v>
       </c>
       <c r="B50">
-        <v>0.9202576565144638</v>
+        <v>0.984267721748924</v>
       </c>
       <c r="C50">
-        <v>1.001772498253766</v>
+        <v>0.9957031590260209</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -957,10 +957,10 @@
         <v>1.566766666666668</v>
       </c>
       <c r="B51">
-        <v>0.9253501896307647</v>
+        <v>0.9844360365091871</v>
       </c>
       <c r="C51">
-        <v>1.001736393786708</v>
+        <v>0.9953780408269338</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -968,10 +968,10 @@
         <v>1.600100000000002</v>
       </c>
       <c r="B52">
-        <v>0.9294802743678904</v>
+        <v>0.9846395521367236</v>
       </c>
       <c r="C52">
-        <v>1.001553859792787</v>
+        <v>0.9950536977632763</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -979,10 +979,10 @@
         <v>1.633433333333335</v>
       </c>
       <c r="B53">
-        <v>0.9325674747114892</v>
+        <v>0.9848658042196101</v>
       </c>
       <c r="C53">
-        <v>1.00124219803103</v>
+        <v>0.9947303414417986</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -990,10 +990,10 @@
         <v>1.666766666666669</v>
       </c>
       <c r="B54">
-        <v>0.9345956853244968</v>
+        <v>0.9851001328191133</v>
       </c>
       <c r="C54">
-        <v>1.000829507491535</v>
+        <v>0.994408121369873</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1001,10 +1001,10 @@
         <v>1.700100000000002</v>
       </c>
       <c r="B55">
-        <v>0.9355447550848972</v>
+        <v>0.9853266972966392</v>
       </c>
       <c r="C55">
-        <v>1.000353251921283</v>
+        <v>0.9940871513294337</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1012,10 +1012,10 @@
         <v>1.733433333333336</v>
       </c>
       <c r="B56">
-        <v>0.9353589414911802</v>
+        <v>0.9855297575528239</v>
       </c>
       <c r="C56">
-        <v>0.999857681593743</v>
+        <v>0.9937675293879196</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1023,10 +1023,10 @@
         <v>1.766766666666669</v>
       </c>
       <c r="B57">
-        <v>0.9339675380741747</v>
+        <v>0.9856950383356277</v>
       </c>
       <c r="C57">
-        <v>0.9993897581405309</v>
+        <v>0.9934493551367276</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1034,10 +1034,10 @@
         <v>1.800100000000002</v>
       </c>
       <c r="B58">
-        <v>0.9313496365656102</v>
+        <v>0.9858109263108724</v>
       </c>
       <c r="C58">
-        <v>0.9989937986550292</v>
+        <v>0.9931327396874815</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1045,10 +1045,10 @@
         <v>1.833433333333336</v>
       </c>
       <c r="B59">
-        <v>0.927611845303436</v>
+        <v>0.9858693249274404</v>
       </c>
       <c r="C59">
-        <v>0.998705781706207</v>
+        <v>0.9928178086651939</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1056,10 +1056,10 @@
         <v>1.866766666666669</v>
       </c>
       <c r="B60">
-        <v>0.9230387832670327</v>
+        <v>0.9858660526022219</v>
       </c>
       <c r="C60">
-        <v>0.9985487099122426</v>
+        <v>0.9925046977665022</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1067,10 +1067,10 @@
         <v>1.900100000000003</v>
       </c>
       <c r="B61">
-        <v>0.9180877829738405</v>
+        <v>0.9858008508439503</v>
       </c>
       <c r="C61">
-        <v>0.9985302751016752</v>
+        <v>0.9921935430160068</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1078,10 +1078,10 @@
         <v>1.933433333333336</v>
       </c>
       <c r="B62">
-        <v>0.9133247594671468</v>
+        <v>0.9856771578535972</v>
       </c>
       <c r="C62">
-        <v>0.9986433214102994</v>
+        <v>0.9918844691779096</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1089,10 +1089,10 @@
         <v>1.96676666666667</v>
       </c>
       <c r="B63">
-        <v>0.9093226864547441</v>
+        <v>0.9855018239749562</v>
       </c>
       <c r="C63">
-        <v>0.9988686165099434</v>
+        <v>0.9915775805354676</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1100,10 +1100,10 @@
         <v>2.000100000000003</v>
       </c>
       <c r="B64">
-        <v>0.9065554485843723</v>
+        <v>0.9852849456042139</v>
       </c>
       <c r="C64">
-        <v>0.999178758064453</v>
+        <v>0.9912729531376383</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1111,10 +1111,10 @@
         <v>2.033433333333336</v>
       </c>
       <c r="B65">
-        <v>0.905316258087706</v>
+        <v>0.985039593243605</v>
       </c>
       <c r="C65">
-        <v>0.999542005078749</v>
+        <v>0.9909706380040827</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1122,10 +1122,10 @@
         <v>2.066766666666669</v>
       </c>
       <c r="B66">
-        <v>0.9056779140321619</v>
+        <v>0.9847816056728571</v>
       </c>
       <c r="C66">
-        <v>0.9999253393696448</v>
+        <v>0.9906706654234554</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>2.100100000000003</v>
       </c>
       <c r="B67">
-        <v>0.9074991853266288</v>
+        <v>0.9845289067889841</v>
       </c>
       <c r="C67">
-        <v>1.00029671001649</v>
+        <v>0.9903730481019454</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1144,10 +1144,10 @@
         <v>2.133433333333336</v>
       </c>
       <c r="B68">
-        <v>0.9104707802310348</v>
+        <v>0.9843003818226108</v>
       </c>
       <c r="C68">
-        <v>1.000626792316868</v>
+        <v>0.9900777888424194</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1155,10 +1155,10 @@
         <v>2.166766666666669</v>
       </c>
       <c r="B69">
-        <v>0.9141863170062402</v>
+        <v>0.9841142442660823</v>
       </c>
       <c r="C69">
-        <v>1.0008905824312</v>
+        <v>0.9897848813201767</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1166,10 +1166,10 @@
         <v>2.200100000000002</v>
       </c>
       <c r="B70">
-        <v>0.91821923871101</v>
+        <v>0.9839860889948935</v>
       </c>
       <c r="C70">
-        <v>1.001068906914173</v>
+        <v>0.9894943069238868</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1177,10 +1177,10 @@
         <v>2.233433333333335</v>
       </c>
       <c r="B71">
-        <v>0.92218711573878</v>
+        <v>0.9839269767661057</v>
       </c>
       <c r="C71">
-        <v>1.001149702105552</v>
+        <v>0.9892060287891508</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1188,10 +1188,10 @@
         <v>2.266766666666669</v>
       </c>
       <c r="B72">
-        <v>0.9257905221440115</v>
+        <v>0.9839419482390722</v>
       </c>
       <c r="C72">
-        <v>1.001128863273547</v>
+        <v>0.9889199862944583</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1199,10 +1199,10 @@
         <v>2.300100000000002</v>
       </c>
       <c r="B73">
-        <v>0.9288227204903973</v>
+        <v>0.9840293414320936</v>
       </c>
       <c r="C73">
-        <v>1.001010552510769</v>
+        <v>0.9886360939027165</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1210,10 +1210,10 @@
         <v>2.333433333333335</v>
       </c>
       <c r="B74">
-        <v>0.9311555200886705</v>
+        <v>0.9841809775355947</v>
       </c>
       <c r="C74">
-        <v>1.00080695410651</v>
+        <v>0.9883542454487174</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -1221,10 +1221,10 @@
         <v>2.366766666666668</v>
       </c>
       <c r="B75">
-        <v>0.9327131509784624</v>
+        <v>0.9843833371741622</v>
       </c>
       <c r="C75">
-        <v>1.000537477800738</v>
+        <v>0.9880743249574495</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1232,10 +1232,10 @@
         <v>2.400100000000001</v>
       </c>
       <c r="B76">
-        <v>0.9334483460957578</v>
+        <v>0.9846192974189892</v>
       </c>
       <c r="C76">
-        <v>1.000227354420219</v>
+        <v>0.9877962191150063</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1243,10 +1243,10 @@
         <v>2.433433333333335</v>
       </c>
       <c r="B77">
-        <v>0.9333324335435917</v>
+        <v>0.9848701513154867</v>
       </c>
       <c r="C77">
-        <v>0.9999055473255285</v>
+        <v>0.9875198284557243</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1254,10 +1254,10 @@
         <v>2.466766666666668</v>
       </c>
       <c r="B78">
-        <v>0.9323643418851305</v>
+        <v>0.9851174807649616</v>
       </c>
       <c r="C78">
-        <v>0.9996020033654356</v>
+        <v>0.9872450735732891</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -1265,10 +1265,10 @@
         <v>2.500100000000001</v>
       </c>
       <c r="B79">
-        <v>0.9305940058231086</v>
+        <v>0.9853445979243126</v>
       </c>
       <c r="C79">
-        <v>0.999344486403391</v>
+        <v>0.9869718954777886</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -1276,10 +1276,10 @@
         <v>2.533433333333334</v>
       </c>
       <c r="B80">
-        <v>0.928147703338321</v>
+        <v>0.9855374433110958</v>
       </c>
       <c r="C80">
-        <v>0.9991554749913588</v>
+        <v>0.9867002515886132</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -1287,10 +1287,10 @@
         <v>2.566766666666668</v>
       </c>
       <c r="B81">
-        <v>0.9252404764655525</v>
+        <v>0.9856850205736993</v>
       </c>
       <c r="C81">
-        <v>0.9990497206042485</v>
+        <v>0.98643010997611</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -1298,10 +1298,10 @@
         <v>2.600100000000001</v>
       </c>
       <c r="B82">
-        <v>0.9221654552352052</v>
+        <v>0.9857795069466501</v>
       </c>
       <c r="C82">
-        <v>0.9990329576043037</v>
+        <v>0.9861614475088915</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -1309,10 +1309,10 @@
         <v>2.633433333333334</v>
       </c>
       <c r="B83">
-        <v>0.9192592120014944</v>
+        <v>0.9858164027983065</v>
       </c>
       <c r="C83">
-        <v>0.9991019507593099</v>
+        <v>0.9858942476679363</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -1320,10 +1320,10 @@
         <v>2.666766666666667</v>
       </c>
       <c r="B84">
-        <v>0.9168514851197977</v>
+        <v>0.9857945782963519</v>
       </c>
       <c r="C84">
-        <v>0.9992456975773342</v>
+        <v>0.9856285045103044</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -1331,10 +1331,10 @@
         <v>2.7001</v>
       </c>
       <c r="B85">
-        <v>0.9152127082025046</v>
+        <v>0.9857164676188893</v>
       </c>
       <c r="C85">
-        <v>0.9994473455752605</v>
+        <v>0.9853642309098303</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -1342,10 +1342,10 @@
         <v>2.733433333333334</v>
       </c>
       <c r="B86">
-        <v>0.9145125484885123</v>
+        <v>0.9855881264030592</v>
       </c>
       <c r="C86">
-        <v>0.9996863414369777</v>
+        <v>0.9851014622434534</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -1353,10 +1353,10 @@
         <v>2.766766666666667</v>
       </c>
       <c r="B87">
-        <v>0.914798859525442</v>
+        <v>0.9854190371070435</v>
       </c>
       <c r="C87">
-        <v>0.9999404668559215</v>
+        <v>0.9848402591933039</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -1364,10 +1364,10 @@
         <v>2.8001</v>
       </c>
       <c r="B88">
-        <v>0.915997368305047</v>
+        <v>0.98522154146685</v>
       </c>
       <c r="C88">
-        <v>1.000187654555557</v>
+        <v>0.9845807053457986</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -1375,10 +1375,10 @@
         <v>2.833433333333333</v>
       </c>
       <c r="B89">
-        <v>0.9179378698807001</v>
+        <v>0.9850098635644909</v>
       </c>
       <c r="C89">
-        <v>1.000407510633229</v>
+        <v>0.9843228997809831</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -1386,10 +1386,10 @@
         <v>2.866766666666666</v>
       </c>
       <c r="B90">
-        <v>0.9203858931034918</v>
+        <v>0.9847989224644182</v>
       </c>
       <c r="C90">
-        <v>1.000582685057643</v>
+        <v>0.9840669457289558</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -1397,10 +1397,10 @@
         <v>2.9001</v>
       </c>
       <c r="B91">
-        <v>0.9230845177774495</v>
+        <v>0.9846030055740347</v>
       </c>
       <c r="C91">
-        <v>1.000700049476191</v>
+        <v>0.9838129394517987</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -1408,10 +1408,10 @@
         <v>2.933433333333333</v>
       </c>
       <c r="B92">
-        <v>0.9257889869529851</v>
+        <v>0.9844346403268586</v>
       </c>
       <c r="C92">
-        <v>1.000751552880339</v>
+        <v>0.9835609607608398</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>2.966766666666666</v>
       </c>
       <c r="B93">
-        <v>0.9282905996675103</v>
+        <v>0.9843037461441926</v>
       </c>
       <c r="C93">
-        <v>1.000734782684354</v>
+        <v>0.9833110675860975</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -1430,10 +1430,10 @@
         <v>3.000099999999999</v>
       </c>
       <c r="B94">
-        <v>0.9304273696055431</v>
+        <v>0.9842171508887302</v>
       </c>
       <c r="C94">
-        <v>1.000653109863698</v>
+        <v>0.9830632942131804</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -1441,10 +1441,10 @@
         <v>3.033433333333333</v>
       </c>
       <c r="B95">
-        <v>0.9320835458844298</v>
+        <v>0.9841784339233566</v>
       </c>
       <c r="C95">
-        <v>1.000515403982003</v>
+        <v>0.9828176512889822</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -1452,10 +1452,10 @@
         <v>3.066766666666666</v>
       </c>
       <c r="B96">
-        <v>0.9331830777600078</v>
+        <v>0.9841880033922167</v>
       </c>
       <c r="C96">
-        <v>1.000335307649985</v>
+        <v>0.9825741253008684</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -1463,10 +1463,10 @@
         <v>3.100099999999999</v>
       </c>
       <c r="B97">
-        <v>0.9336830093319052</v>
+        <v>0.984243309784201</v>
       </c>
       <c r="C97">
-        <v>1.000130074088877</v>
+        <v>0.9823326762173658</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -1474,10 +1474,10 @@
         <v>3.133433333333332</v>
       </c>
       <c r="B98">
-        <v>0.9335713956959434</v>
+        <v>0.9843391374023722</v>
       </c>
       <c r="C98">
-        <v>0.99991900446419</v>
+        <v>0.9820932338521737</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -1485,10 +1485,10 @@
         <v>3.166766666666665</v>
       </c>
       <c r="B99">
-        <v>0.9328711388924128</v>
+        <v>0.9844679734922838</v>
       </c>
       <c r="C99">
-        <v>0.9997215886651736</v>
+        <v>0.981855695253001</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -1496,10 +1496,10 @@
         <v>3.200099999999999</v>
       </c>
       <c r="B100">
-        <v>0.9316473743073713</v>
+        <v>0.9846204973977123</v>
       </c>
       <c r="C100">
-        <v>0.9995555426101158</v>
+        <v>0.9816199260754135</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -1507,10 +1507,10 @@
         <v>3.233433333333332</v>
       </c>
       <c r="B101">
-        <v>0.9300133160242535</v>
+        <v>0.9847862322185303</v>
       </c>
       <c r="C101">
-        <v>0.9994350080541498</v>
+        <v>0.9813857680348967</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -1518,10 +1518,10 @@
         <v>3.266766666666665</v>
       </c>
       <c r="B102">
-        <v>0.9281290813148612</v>
+        <v>0.984954354667867</v>
       </c>
       <c r="C102">
-        <v>0.9993691922329179</v>
+        <v>0.9811530525555691</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -1529,10 +1529,10 @@
         <v>3.300099999999998</v>
       </c>
       <c r="B103">
-        <v>0.9261901852916073</v>
+        <v>0.9851145835961478</v>
       </c>
       <c r="C103">
-        <v>0.9993616523486324</v>
+        <v>0.9809216184753796</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -1540,10 +1540,10 @@
         <v>3.333433333333331</v>
       </c>
       <c r="B104">
-        <v>0.9244061189961575</v>
+        <v>0.9852580021112739</v>
       </c>
       <c r="C104">
-        <v>0.9994102925767977</v>
+        <v>0.9806913300364642</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -1551,10 +1551,10 @@
         <v>3.366766666666665</v>
       </c>
       <c r="B105">
-        <v>0.9229730289757433</v>
+        <v>0.985377648777801</v>
       </c>
       <c r="C105">
-        <v>0.9995079916716147</v>
+        <v>0.980462091087048</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -1562,10 +1562,10 @@
         <v>3.400099999999998</v>
       </c>
       <c r="B106">
-        <v>0.9220465815245366</v>
+        <v>0.9854687584877534</v>
       </c>
       <c r="C106">
-        <v>0.9996436751591004</v>
+        <v>0.9802338524913184</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -1573,10 +1573,10 @@
         <v>3.433433333333331</v>
       </c>
       <c r="B107">
-        <v>0.9217210638654556</v>
+        <v>0.9855286322474444</v>
       </c>
       <c r="C107">
-        <v>0.9998036180198147</v>
+        <v>0.9800066117529866</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -1584,10 +1584,10 @@
         <v>3.466766666666664</v>
       </c>
       <c r="B108">
-        <v>0.9220191047873572</v>
+        <v>0.985556232825043</v>
       </c>
       <c r="C108">
-        <v>0.9999727974430994</v>
+        <v>0.97978040635642</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -1595,10 +1595,10 @@
         <v>3.500099999999998</v>
       </c>
       <c r="B109">
-        <v>0.9228925810628936</v>
+        <v>0.9855516837754376</v>
       </c>
       <c r="C109">
-        <v>1.000136208937332</v>
+        <v>0.9795553033787525</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -1606,10 +1606,10 @@
         <v>3.533433333333331</v>
       </c>
       <c r="B110">
-        <v>0.9242361301163676</v>
+        <v>0.985515878721124</v>
       </c>
       <c r="C110">
-        <v>1.000280015450989</v>
+        <v>0.9793313892114576</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -1617,10 +1617,10 @@
         <v>3.566766666666664</v>
       </c>
       <c r="B111">
-        <v>0.9259050875190972</v>
+        <v>0.9854503397716782</v>
       </c>
       <c r="C111">
-        <v>1.000392587398125</v>
+        <v>0.9791087621138572</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -1628,10 +1628,10 @@
         <v>3.600099999999997</v>
       </c>
       <c r="B112">
-        <v>0.9277378420206</v>
+        <v>0.9853573603264517</v>
       </c>
       <c r="C112">
-        <v>1.000465356941877</v>
+        <v>0.9788875279540882</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -1639,10 +1639,10 @@
         <v>3.63343333333333</v>
       </c>
       <c r="B113">
-        <v>0.9295754389728783</v>
+        <v>0.9852403390461655</v>
       </c>
       <c r="C113">
-        <v>1.000493386516697</v>
+        <v>0.9786677979919332</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -1650,10 +1650,10 @@
         <v>3.666766666666664</v>
       </c>
       <c r="B114">
-        <v>0.9312762874358783</v>
+        <v>0.9851041402311554</v>
       </c>
       <c r="C114">
-        <v>1.000475705773493</v>
+        <v>0.9784496874194901</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -1661,10 +1661,10 @@
         <v>3.700099999999997</v>
       </c>
       <c r="B115">
-        <v>0.9327247466483786</v>
+        <v>0.9849552670220451</v>
       </c>
       <c r="C115">
-        <v>1.000415324500628</v>
+        <v>0.978233310425901</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -1672,10 +1672,10 @@
         <v>3.73343333333333</v>
       </c>
       <c r="B116">
-        <v>0.9338344171262083</v>
+        <v>0.9848017374524701</v>
       </c>
       <c r="C116">
-        <v>1.000318926591949</v>
+        <v>0.9780187708936579</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -1683,10 +1683,10 @@
         <v>3.766766666666663</v>
       </c>
       <c r="B117">
-        <v>0.9345482394714216</v>
+        <v>0.9846526180080797</v>
       </c>
       <c r="C117">
-        <v>1.0001962506762</v>
+        <v>0.9778061507215247</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -1694,10 +1694,10 @@
         <v>3.800099999999996</v>
       </c>
       <c r="B118">
-        <v>0.9348377961733425</v>
+        <v>0.9845173020597927</v>
       </c>
       <c r="C118">
-        <v>1.000059185684581</v>
+        <v>0.9775954966880631</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -1705,10 +1705,10 @@
         <v>3.83343333333333</v>
       </c>
       <c r="B119">
-        <v>0.934703346213519</v>
+        <v>0.9844046865273515</v>
       </c>
       <c r="C119">
-        <v>0.999920658194834</v>
+        <v>0.977386810122028</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -1716,10 +1716,10 @@
         <v>3.866766666666663</v>
       </c>
       <c r="B120">
-        <v>0.9341751755640686</v>
+        <v>0.9843224269556011</v>
       </c>
       <c r="C120">
-        <v>0.9997933696902458</v>
+        <v>0.977180042274468</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -1727,10 +1727,10 @@
         <v>3.900099999999996</v>
       </c>
       <c r="B121">
-        <v>0.9333145264226779</v>
+        <v>0.9842762850484472</v>
       </c>
       <c r="C121">
-        <v>0.9996885707552636</v>
+        <v>0.9769750990443694</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -1738,10 +1738,10 @@
         <v>3.933433333333329</v>
       </c>
       <c r="B122">
-        <v>0.9322125963229423</v>
+        <v>0.9842699190075506</v>
       </c>
       <c r="C122">
-        <v>0.9996150046039688</v>
+        <v>0.9767718501200379</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -1749,10 +1749,10 @@
         <v>3.966766666666663</v>
       </c>
       <c r="B123">
-        <v>0.9309853035173005</v>
+        <v>0.9843045675914432</v>
       </c>
       <c r="C123">
-        <v>0.9995781205136167</v>
+        <v>0.9765701447034143</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -1760,10 +1760,10 @@
         <v>4.000099999999996</v>
       </c>
       <c r="B124">
-        <v>0.9297640070684239</v>
+        <v>0.9843790772477936</v>
       </c>
       <c r="C124">
-        <v>0.9995797005027947</v>
+        <v>0.9763698299075249</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -1771,10 +1771,10 @@
         <v>4.033433333333329</v>
       </c>
       <c r="B125">
-        <v>0.9286803867821133</v>
+        <v>0.9844899020287309</v>
       </c>
       <c r="C125">
-        <v>0.9996178921747035</v>
+        <v>0.9761707635331648</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -1782,10 +1782,10 @@
         <v>4.066766666666663</v>
       </c>
       <c r="B126">
-        <v>0.927852029850388</v>
+        <v>0.9846311680855818</v>
       </c>
       <c r="C126">
-        <v>0.9996876100221688</v>
+        <v>0.975972823690001</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -1793,10 +1793,10 @@
         <v>4.100099999999996</v>
       </c>
       <c r="B127">
-        <v>0.92736742788182</v>
+        <v>0.9847948250074857</v>
       </c>
       <c r="C127">
-        <v>0.9997812077266393</v>
+        <v>0.9757759130895112</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -1804,10 +1804,10 @@
         <v>4.133433333333329</v>
       </c>
       <c r="B128">
-        <v>0.9272757314810662</v>
+        <v>0.9849709531079556</v>
       </c>
       <c r="C128">
-        <v>0.9998893219403844</v>
+        <v>0.975579959779649</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -1815,10 +1815,10 @@
         <v>4.166766666666662</v>
       </c>
       <c r="B129">
-        <v>0.927582337642435</v>
+        <v>0.9851482863108363</v>
       </c>
       <c r="C129">
-        <v>1.00000178443234</v>
+        <v>0.9753849165544222</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -1826,10 +1826,10 @@
         <v>4.200099999999996</v>
       </c>
       <c r="B130">
-        <v>0.9282506631424688</v>
+        <v>0.9853149580660328</v>
       </c>
       <c r="C130">
-        <v>1.000108533817991</v>
+        <v>0.9751907611835418</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -1837,10 +1837,10 @@
         <v>4.233433333333329</v>
       </c>
       <c r="B131">
-        <v>0.9292100215725428</v>
+        <v>0.9854594324504109</v>
       </c>
       <c r="C131">
-        <v>1.000200427987655</v>
+        <v>0.9749974967130748</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -1848,10 +1848,10 @@
         <v>4.266766666666662</v>
       </c>
       <c r="B132">
-        <v>0.930366380967295</v>
+        <v>0.9855714354486091</v>
       </c>
       <c r="C132">
-        <v>1.000269970427075</v>
+        <v>0.974805152722033</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -1859,10 +1859,10 @@
         <v>4.300099999999995</v>
       </c>
       <c r="B133">
-        <v>0.9316149705256291</v>
+        <v>0.9856428266715845</v>
       </c>
       <c r="C133">
-        <v>1.00031188411833</v>
+        <v>0.9746137843971887</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -1870,10 +1870,10 @@
         <v>4.333433333333328</v>
       </c>
       <c r="B134">
-        <v>0.9328517752281471</v>
+        <v>0.9856682206469981</v>
       </c>
       <c r="C134">
-        <v>1.000323465302813</v>
+        <v>0.9744234680453129</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -1881,10 +1881,10 @@
         <v>4.366766666666662</v>
       </c>
       <c r="B135">
-        <v>0.9339828869680239</v>
+        <v>0.9856453011386233</v>
       </c>
       <c r="C135">
-        <v>1.000304753477005</v>
+        <v>0.9742342936376535</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -1892,10 +1892,10 @@
         <v>4.400099999999995</v>
       </c>
       <c r="B136">
-        <v>0.9349299928352303</v>
+        <v>0.9855748838965666</v>
       </c>
       <c r="C136">
-        <v>1.000258460691448</v>
+        <v>0.9740463554691252</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -1903,10 +1903,10 @@
         <v>4.433433333333328</v>
       </c>
       <c r="B137">
-        <v>0.9356349976420487</v>
+        <v>0.9854607851945705</v>
       </c>
       <c r="C137">
-        <v>1.000189685968074</v>
+        <v>0.9738597417529005</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -1914,10 +1914,10 @@
         <v>4.466766666666661</v>
       </c>
       <c r="B138">
-        <v>0.9360611653763797</v>
+        <v>0.9853095989070723</v>
       </c>
       <c r="C138">
-        <v>1.00010540602189</v>
+        <v>0.9736745269474872</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -1925,10 +1925,10 @@
         <v>4.500099999999994</v>
       </c>
       <c r="B139">
-        <v>0.9361940093598993</v>
+        <v>0.9851304586920787</v>
       </c>
       <c r="C139">
-        <v>1.000013798443326</v>
+        <v>0.973490765188178</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -1936,10 +1936,10 @@
         <v>4.533433333333328</v>
       </c>
       <c r="B140">
-        <v>0.9360415728797599</v>
+        <v>0.9849346862308155</v>
       </c>
       <c r="C140">
-        <v>0.9999234679181332</v>
+        <v>0.9733084917762054</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -1947,10 +1947,10 @@
         <v>4.566766666666661</v>
       </c>
       <c r="B141">
-        <v>0.9356341905883051</v>
+        <v>0.9847353772506848</v>
       </c>
       <c r="C141">
-        <v>0.9998426227352393</v>
+        <v>0.9731277253237404</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -1958,10 +1958,10 @@
         <v>4.600099999999994</v>
       </c>
       <c r="B142">
-        <v>0.9350231880910331</v>
+        <v>0.9845466853938241</v>
       </c>
       <c r="C142">
-        <v>0.9997783036353936</v>
+        <v>0.9729484690890409</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -1969,10 +1969,10 @@
         <v>4.633433333333327</v>
       </c>
       <c r="B143">
-        <v>0.9342777952828737</v>
+        <v>0.9843828286683213</v>
       </c>
       <c r="C143">
-        <v>0.9997357486348493</v>
+        <v>0.9727707159808671</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -1980,10 +1980,10 @@
         <v>4.666766666666661</v>
       </c>
       <c r="B144">
-        <v>0.9334797829013007</v>
+        <v>0.984256830664437</v>
       </c>
       <c r="C144">
-        <v>0.9997179634443292</v>
+        <v>0.9725944491974176</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -1991,10 +1991,10 @@
         <v>4.700099999999994</v>
       </c>
       <c r="B145">
-        <v>0.9327159556566472</v>
+        <v>0.9841791516859375</v>
       </c>
       <c r="C145">
-        <v>0.9997255434992501</v>
+        <v>0.9724196408881236</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -2002,10 +2002,10 @@
         <v>4.733433333333327</v>
       </c>
       <c r="B146">
-        <v>0.9320689433022937</v>
+        <v>0.9841564496416818</v>
       </c>
       <c r="C146">
-        <v>0.9997567204723322</v>
+        <v>0.9722462493951772</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -2013,10 +2013,10 @@
         <v>4.76676666666666</v>
       </c>
       <c r="B147">
-        <v>0.931608517012762</v>
+        <v>0.9841906733247061</v>
       </c>
       <c r="C147">
-        <v>0.9998076706548878</v>
+        <v>0.9720742180230358</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -2024,10 +2024,10 @@
         <v>4.800099999999993</v>
       </c>
       <c r="B148">
-        <v>0.9313835997853146</v>
+        <v>0.9842788668036453</v>
       </c>
       <c r="C148">
-        <v>0.9998729841185222</v>
+        <v>0.971903475206342</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -2035,10 +2035,10 @@
         <v>4.833433333333327</v>
       </c>
       <c r="B149">
-        <v>0.9314173871121241</v>
+        <v>0.9844133757676249</v>
       </c>
       <c r="C149">
-        <v>0.9999462080375929</v>
+        <v>0.9717339383091128</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -2046,10 +2046,10 @@
         <v>4.86676666666666</v>
       </c>
       <c r="B150">
-        <v>0.9317057491097398</v>
+        <v>0.984582896198251</v>
       </c>
       <c r="C150">
-        <v>1.000020495702387</v>
+        <v>0.971565522379472</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -2057,10 +2057,10 @@
         <v>4.900099999999993</v>
       </c>
       <c r="B151">
-        <v>0.9322193813478906</v>
+        <v>0.984773748100596</v>
       </c>
       <c r="C151">
-        <v>1.000089191523817</v>
+        <v>0.9713981475109174</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -2068,10 +2068,10 @@
         <v>4.933433333333326</v>
       </c>
       <c r="B152">
-        <v>0.9329086387266159</v>
+        <v>0.984971338478882</v>
       </c>
       <c r="C152">
-        <v>1.000146399382392</v>
+        <v>0.9712317457003535</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -2079,10 +2079,10 @@
         <v>4.966766666666659</v>
       </c>
       <c r="B153">
-        <v>0.9337103586300352</v>
+        <v>0.9851614934113588</v>
       </c>
       <c r="C153">
-        <v>1.000187482963783</v>
+        <v>0.9710662643499587</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -2090,10 +2090,10 @@
         <v>5.000099999999993</v>
       </c>
       <c r="B154">
-        <v>0.9345553333463632</v>
+        <v>0.9853314926327579</v>
       </c>
       <c r="C154">
-        <v>1.000209392856866</v>
+        <v>0.9709016660840151</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -2101,10 +2101,10 @@
         <v>5.033433333333326</v>
       </c>
       <c r="B155">
-        <v>0.9353753057951293</v>
+        <v>0.9854707519389819</v>
       </c>
       <c r="C155">
-        <v>1.000210883485659</v>
+        <v>0.9707379256318844</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -2112,10 +2112,10 @@
         <v>5.066766666666659</v>
       </c>
       <c r="B156">
-        <v>0.9361088918141094</v>
+        <v>0.9855711754198611</v>
       </c>
       <c r="C156">
-        <v>1.000192572313082</v>
+        <v>0.9705750276635666</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -2123,10 +2123,10 @@
         <v>5.100099999999992</v>
       </c>
       <c r="B157">
-        <v>0.9367054615510799</v>
+        <v>0.9856273706133989</v>
       </c>
       <c r="C157">
-        <v>1.000156824993359</v>
+        <v>0.9704129635842846</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -2134,10 +2134,10 @@
         <v>5.133433333333326</v>
       </c>
       <c r="B158">
-        <v>0.9371286194072931</v>
+        <v>0.9856367422772788</v>
       </c>
       <c r="C158">
-        <v>1.000107508126125</v>
+        <v>0.9702517306307309</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -2145,10 +2145,10 @@
         <v>5.166766666666659</v>
       </c>
       <c r="B159">
-        <v>0.937357495939309</v>
+        <v>0.985599579315639</v>
       </c>
       <c r="C159">
-        <v>1.000049597495583</v>
+        <v>0.9700913362835648</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -2156,10 +2156,10 @@
         <v>5.200099999999992</v>
       </c>
       <c r="B160">
-        <v>0.937387576441552</v>
+        <v>0.9855191134825001</v>
       </c>
       <c r="C160">
-        <v>0.9999886824177446</v>
+        <v>0.9699318015621022</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -2167,10 +2167,10 @@
         <v>5.233433333333325</v>
       </c>
       <c r="B161">
-        <v>0.9372306352407763</v>
+        <v>0.9854014433684394</v>
       </c>
       <c r="C161">
-        <v>0.9999304404739351</v>
+        <v>0.9697731634938623</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -2178,10 +2178,10 @@
         <v>5.266766666666658</v>
       </c>
       <c r="B162">
-        <v>0.9369137983935211</v>
+        <v>0.9852552353283595</v>
       </c>
       <c r="C162">
-        <v>0.9998801018935979</v>
+        <v>0.969615475985206</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -2189,10 +2189,10 @@
         <v>5.300099999999992</v>
       </c>
       <c r="B163">
-        <v>0.9364775405244891</v>
+        <v>0.9850911394522648</v>
       </c>
       <c r="C163">
-        <v>0.999841972537103</v>
+        <v>0.9694588075653653</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -2200,10 +2200,10 @@
         <v>5.333433333333325</v>
       </c>
       <c r="B164">
-        <v>0.9359724464741328</v>
+        <v>0.9849209374514387</v>
       </c>
       <c r="C164">
-        <v>0.9998190626752812</v>
+        <v>0.9693032354272644</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -2211,10 +2211,10 @@
         <v>5.366766666666658</v>
       </c>
       <c r="B165">
-        <v>0.9354548125162911</v>
+        <v>0.9847565804249031</v>
       </c>
       <c r="C165">
-        <v>0.9998128619420653</v>
+        <v>0.9691488371563599</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -2222,10 +2222,10 @@
         <v>5.400099999999991</v>
       </c>
       <c r="B166">
-        <v>0.9349810253615607</v>
+        <v>0.9846091331334044</v>
       </c>
       <c r="C166">
-        <v>0.9998232513177272</v>
+        <v>0.9689956833810119</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -2233,10 +2233,10 @@
         <v>5.433433333333324</v>
       </c>
       <c r="B167">
-        <v>0.9346022635097773</v>
+        <v>0.9844879322205707</v>
       </c>
       <c r="C167">
-        <v>0.9998486052151297</v>
+        <v>0.9688438308767031</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -2244,10 +2244,10 @@
         <v>5.466766666666658</v>
       </c>
       <c r="B168">
-        <v>0.9343589671323602</v>
+        <v>0.9843999634631263</v>
       </c>
       <c r="C168">
-        <v>0.9998860204672703</v>
+        <v>0.9686933186573347</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -2255,10 +2255,10 @@
         <v>5.500099999999991</v>
       </c>
       <c r="B169">
-        <v>0.9342768680212422</v>
+        <v>0.9843495357122496</v>
       </c>
       <c r="C169">
-        <v>0.9999316195740904</v>
+        <v>0.9685441663784279</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -2266,10 +2266,10 @@
         <v>5.533433333333324</v>
       </c>
       <c r="B170">
-        <v>0.9343647617272112</v>
+        <v>0.9843382212475393</v>
       </c>
       <c r="C170">
-        <v>0.9999809735573295</v>
+        <v>0.9683963739838051</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -2277,10 +2277,10 @@
         <v>5.566766666666657</v>
       </c>
       <c r="B171">
-        <v>0.934614314721725</v>
+        <v>0.9843649966435394</v>
       </c>
       <c r="C171">
-        <v>1.000029497359259</v>
+        <v>0.9682499213303518</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -2288,10 +2288,10 @@
         <v>5.600099999999991</v>
       </c>
       <c r="B172">
-        <v>0.935001898638058</v>
+        <v>0.984426511494701</v>
       </c>
       <c r="C172">
-        <v>1.000072859788469</v>
+        <v>0.9681047671571203</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -2299,10 +2299,10 @@
         <v>5.633433333333324</v>
       </c>
       <c r="B173">
-        <v>0.9354919438834747</v>
+        <v>0.9845174213387263</v>
       </c>
       <c r="C173">
-        <v>1.000107374696194</v>
+        <v>0.9679608481656887</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -2310,10 +2310,10 @@
         <v>5.666766666666657</v>
       </c>
       <c r="B174">
-        <v>0.9360413214504799</v>
+        <v>0.9846308628423706</v>
       </c>
       <c r="C174">
-        <v>1.000130293314087</v>
+        <v>0.967818077595624</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -2321,10 +2321,10 @@
         <v>5.70009999999999</v>
       </c>
       <c r="B175">
-        <v>0.936604011042107</v>
+        <v>0.9847587999873891</v>
       </c>
       <c r="C175">
-        <v>1.00014000780122</v>
+        <v>0.967676349727591</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -2332,10 +2332,10 @@
         <v>5.733433333333323</v>
       </c>
       <c r="B176">
-        <v>0.9371353474384657</v>
+        <v>0.9848927173075389</v>
       </c>
       <c r="C176">
-        <v>1.000136135640627</v>
+        <v>0.9675355463328467</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -2343,10 +2343,10 @@
         <v>5.766766666666657</v>
       </c>
       <c r="B177">
-        <v>0.9375959574012381</v>
+        <v>0.985024175645057</v>
       </c>
       <c r="C177">
-        <v>1.000119542394219</v>
+        <v>0.9673955450268217</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -2354,10 +2354,10 @@
         <v>5.80009999999999</v>
       </c>
       <c r="B178">
-        <v>0.9379545168885428</v>
+        <v>0.9851454521501565</v>
       </c>
       <c r="C178">
-        <v>1.000092221456288</v>
+        <v>0.9672562329537696</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -2365,10 +2365,10 @@
         <v>5.833433333333323</v>
       </c>
       <c r="B179">
-        <v>0.938189763133582</v>
+        <v>0.9852500794355212</v>
       </c>
       <c r="C179">
-        <v>1.000057061211601</v>
+        <v>0.9671175183727727</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -2376,10 +2376,10 @@
         <v>5.866766666666656</v>
       </c>
       <c r="B180">
-        <v>0.9382916325711159</v>
+        <v>0.9853332028994336</v>
       </c>
       <c r="C180">
-        <v>1.000017565656972</v>
+        <v>0.9669793397156071</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -2387,10 +2387,10 @@
         <v>5.900099999999989</v>
       </c>
       <c r="B181">
-        <v>0.9382616161752199</v>
+        <v>0.9853916956212776</v>
       </c>
       <c r="C181">
-        <v>0.9999775116190548</v>
+        <v>0.9668416699743163</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -2398,10 +2398,10 @@
         <v>5.933433333333323</v>
       </c>
       <c r="B182">
-        <v>0.9381123528683257</v>
+        <v>0.985424039404918</v>
       </c>
       <c r="C182">
-        <v>0.9999405899949613</v>
+        <v>0.9667045166366286</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -2409,10 +2409,10 @@
         <v>5.966766666666656</v>
       </c>
       <c r="B183">
-        <v>0.9378664428553627</v>
+        <v>0.9854300306941748</v>
       </c>
       <c r="C183">
-        <v>0.999910065481745</v>
+        <v>0.9665679165551195</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -2420,10 +2420,10 @@
         <v>6.000099999999989</v>
       </c>
       <c r="B184">
-        <v>0.9375544631366632</v>
+        <v>0.9854104493659732</v>
       </c>
       <c r="C184">
-        <v>0.9998884878929833</v>
+        <v>0.9664319287891333</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -2431,10 +2431,10 @@
         <v>6.033433333333322</v>
       </c>
       <c r="B185">
-        <v>0.9372122305120774</v>
+        <v>0.9853667952148439</v>
       </c>
       <c r="C185">
-        <v>0.9998774824229663</v>
+        <v>0.9662966283586727</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -2442,10 +2442,10 @@
         <v>6.066766666666656</v>
       </c>
       <c r="B186">
-        <v>0.9368774740940121</v>
+        <v>0.9853011803245729</v>
       </c>
       <c r="C186">
-        <v>0.999877636815592</v>
+        <v>0.9661620998016912</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -2453,10 +2453,10 @@
         <v>6.100099999999989</v>
       </c>
       <c r="B187">
-        <v>0.9365862140028111</v>
+        <v>0.9852163827040856</v>
       </c>
       <c r="C187">
-        <v>0.9998884920032188</v>
+        <v>0.9660284334406616</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -2464,10 +2464,10 @@
         <v>6.133433333333322</v>
       </c>
       <c r="B188">
-        <v>0.9363692481143948</v>
+        <v>0.9851160070157688</v>
       </c>
       <c r="C188">
-        <v>0.9999086313299882</v>
+        <v>0.965895722675597</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -2475,10 +2475,10 @@
         <v>6.166766666666655</v>
       </c>
       <c r="B189">
-        <v>0.9362491838372267</v>
+        <v>0.9850046210558012</v>
       </c>
       <c r="C189">
-        <v>0.9999358537217615</v>
+        <v>0.9657640605472664</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -2486,10 +2486,10 @@
         <v>6.200099999999988</v>
       </c>
       <c r="B190">
-        <v>0.9362383980742811</v>
+        <v>0.984887779792008</v>
       </c>
       <c r="C190">
-        <v>0.9999674092382432</v>
+        <v>0.9656335343176862</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -2497,10 +2497,10 @@
         <v>6.233433333333322</v>
       </c>
       <c r="B191">
-        <v>0.9363381744082458</v>
+        <v>0.9847718479559865</v>
       </c>
       <c r="C191">
-        <v>1.000000271683061</v>
+        <v>0.9655042185673611</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -2508,10 +2508,10 @@
         <v>6.266766666666655</v>
       </c>
       <c r="B192">
-        <v>0.9365390839780712</v>
+        <v>0.9846636224313878</v>
       </c>
       <c r="C192">
-        <v>1.000031422043941</v>
+        <v>0.96537616635206</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -2519,10 +2519,10 @@
         <v>6.300099999999988</v>
       </c>
       <c r="B193">
-        <v>0.936822489216707</v>
+        <v>0.9845698145605071</v>
       </c>
       <c r="C193">
-        <v>1.000058117853995</v>
+        <v>0.9652494007849289</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -2530,10 +2530,10 @@
         <v>6.333433333333321</v>
       </c>
       <c r="B194">
-        <v>0.9371628994623549</v>
+        <v>0.984496493699013</v>
       </c>
       <c r="C194">
-        <v>1.000078126475227</v>
+        <v>0.9651239092681441</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -2541,10 +2541,10 @@
         <v>6.366766666666654</v>
       </c>
       <c r="B195">
-        <v>0.9375308227847592</v>
+        <v>0.9844486019536337</v>
       </c>
       <c r="C195">
-        <v>1.000089904355795</v>
+        <v>0.9649996419507618</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -2552,10 +2552,10 @@
         <v>6.400099999999988</v>
       </c>
       <c r="B196">
-        <v>0.9378957475403062</v>
+        <v>0.984429559694243</v>
       </c>
       <c r="C196">
-        <v>1.000092709239711</v>
+        <v>0.9648765173922847</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -2563,10 +2563,10 @@
         <v>6.433433333333321</v>
       </c>
       <c r="B197">
-        <v>0.9382289385501157</v>
+        <v>0.9844411311146112</v>
       </c>
       <c r="C197">
-        <v>1.000086637932584</v>
+        <v>0.9647544295974321</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -2574,10 +2574,10 @@
         <v>6.466766666666654</v>
       </c>
       <c r="B198">
-        <v>0.93850582066374</v>
+        <v>0.9844832753531675</v>
       </c>
       <c r="C198">
-        <v>1.000072588342047</v>
+        <v>0.9646332599296462</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -2585,10 +2585,10 @@
         <v>6.500099999999987</v>
       </c>
       <c r="B199">
-        <v>0.9387078166173947</v>
+        <v>0.9845541879684523</v>
       </c>
       <c r="C199">
-        <v>1.000052150814897</v>
+        <v>0.9645128911840448</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -2596,10 +2596,10 @@
         <v>6.533433333333321</v>
       </c>
       <c r="B200">
-        <v>0.9388235818715045</v>
+        <v>0.9846503465079107</v>
       </c>
       <c r="C200">
-        <v>1.000027439871542</v>
+        <v>0.964393216137416</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -2607,10 +2607,10 @@
         <v>6.566766666666654</v>
       </c>
       <c r="B201">
-        <v>0.9388496246845446</v>
+        <v>0.9847666030776998</v>
       </c>
       <c r="C201">
-        <v>1.000000882780977</v>
+        <v>0.9642741446634664</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -2618,10 +2618,10 @@
         <v>6.600099999999987</v>
       </c>
       <c r="B202">
-        <v>0.938790318143611</v>
+        <v>0.9848963423209542</v>
       </c>
       <c r="C202">
-        <v>0.9999749853621952</v>
+        <v>0.9641556071155012</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -2629,10 +2629,10 @@
         <v>6.63343333333332</v>
       </c>
       <c r="B203">
-        <v>0.9386573167335108</v>
+        <v>0.985031748525493</v>
       </c>
       <c r="C203">
-        <v>0.9999520982601012</v>
+        <v>0.964037555221717</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -2640,10 +2640,10 @@
         <v>6.666766666666653</v>
       </c>
       <c r="B204">
-        <v>0.938468401555216</v>
+        <v>0.9851642124201981</v>
       </c>
       <c r="C204">
-        <v>0.9999342042957583</v>
+        <v>0.9639199618478761</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -2651,10 +2651,10 @@
         <v>6.700099999999987</v>
       </c>
       <c r="B205">
-        <v>0.9382458088767642</v>
+        <v>0.9852849115552571</v>
       </c>
       <c r="C205">
-        <v>0.9999227498203584</v>
+        <v>0.9638028208888013</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -2662,10 +2662,10 @@
         <v>6.73343333333332</v>
       </c>
       <c r="B206">
-        <v>0.9380141485757333</v>
+        <v>0.9853854378736459</v>
       </c>
       <c r="C206">
-        <v>0.9999185319190788</v>
+        <v>0.9636861469067058</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -2673,10 +2673,10 @@
         <v>6.766766666666653</v>
       </c>
       <c r="B207">
-        <v>0.9377980820440394</v>
+        <v>0.985458509869485</v>
       </c>
       <c r="C207">
-        <v>0.9999216518144368</v>
+        <v>0.9635699745641171</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -2684,10 +2684,10 @@
         <v>6.800099999999986</v>
       </c>
       <c r="B208">
-        <v>0.9376199845908618</v>
+        <v>0.9854985716954133</v>
       </c>
       <c r="C208">
-        <v>0.9999315352098155</v>
+        <v>0.9634543569961975</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -2695,10 +2695,10 @@
         <v>6.833433333333319</v>
       </c>
       <c r="B209">
-        <v>0.9374978453933439</v>
+        <v>0.9855022476409956</v>
       </c>
       <c r="C209">
-        <v>0.9999470142333019</v>
+        <v>0.9633393617058068</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -2706,10 +2706,10 @@
         <v>6.866766666666653</v>
       </c>
       <c r="B210">
-        <v>0.9374436450835255</v>
+        <v>0.9854685817330077</v>
       </c>
       <c r="C210">
-        <v>0.9999664599295526</v>
+        <v>0.9632250642801563</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -2717,10 +2717,10 @@
         <v>6.900099999999986</v>
       </c>
       <c r="B211">
-        <v>0.9374623949309441</v>
+        <v>0.9853990927878916</v>
       </c>
       <c r="C211">
-        <v>0.9999879503029094</v>
+        <v>0.9631115409986353</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -2728,10 +2728,10 @@
         <v>6.933433333333319</v>
       </c>
       <c r="B212">
-        <v>0.9375519321664901</v>
+        <v>0.9852976718537207</v>
       </c>
       <c r="C212">
-        <v>1.000009456808344</v>
+        <v>0.96299886221646</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -2739,10 +2739,10 @@
         <v>6.966766666666652</v>
       </c>
       <c r="B213">
-        <v>0.9377034619607404</v>
+        <v>0.9851703822376111</v>
       </c>
       <c r="C213">
-        <v>1.000029031800332</v>
+        <v>0.9628870852046292</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -2750,10 +2750,10 @@
         <v>7.000099999999986</v>
       </c>
       <c r="B214">
-        <v>0.9379027395551867</v>
+        <v>0.9850251771520788</v>
       </c>
       <c r="C214">
-        <v>1.000044980518471</v>
+        <v>0.9627762513535241</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -2761,10 +2761,10 @@
         <v>7.033433333333319</v>
       </c>
       <c r="B215">
-        <v>0.9381317144524515</v>
+        <v>0.9848715300311218</v>
       </c>
       <c r="C215">
-        <v>1.000056003415643</v>
+        <v>0.9626663861684154</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -2772,10 +2772,10 @@
         <v>7.066766666666652</v>
       </c>
       <c r="B216">
-        <v>0.9383704229098815</v>
+        <v>0.9847199754000582</v>
       </c>
       <c r="C216">
-        <v>1.000061297753296</v>
+        <v>0.9625575002087791</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -2783,10 +2783,10 @@
         <v>7.100099999999985</v>
       </c>
       <c r="B217">
-        <v>0.9385989159684842</v>
+        <v>0.9845814326426016</v>
       </c>
       <c r="C217">
-        <v>1.000060611166973</v>
+        <v>0.9624495912201525</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -2794,10 +2794,10 @@
         <v>7.133433333333318</v>
       </c>
       <c r="B218">
-        <v>0.9387990399731907</v>
+        <v>0.984466399779301</v>
       </c>
       <c r="C218">
-        <v>1.000054244118226</v>
+        <v>0.9623426461936452</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -2805,10 +2805,10 @@
         <v>7.166766666666652</v>
       </c>
       <c r="B219">
-        <v>0.9389559320207251</v>
+        <v>0.984384010222589</v>
       </c>
       <c r="C219">
-        <v>1.000043002545886</v>
+        <v>0.9622366432771077</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -2816,10 +2816,10 @@
         <v>7.200099999999985</v>
       </c>
       <c r="B220">
-        <v>0.9390591406279503</v>
+        <v>0.9843410965443818</v>
       </c>
       <c r="C220">
-        <v>1.000028106317479</v>
+        <v>0.9621315512287861</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -2827,10 +2827,10 @@
         <v>7.233433333333318</v>
       </c>
       <c r="B221">
-        <v>0.9391033225244897</v>
+        <v>0.9843413530074264</v>
       </c>
       <c r="C221">
-        <v>1.000011062926104</v>
+        <v>0.9620273297886529</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -2838,10 +2838,10 @@
         <v>7.266766666666651</v>
       </c>
       <c r="B222">
-        <v>0.9390884963100693</v>
+        <v>0.9843849277358541</v>
       </c>
       <c r="C222">
-        <v>0.9999935189246255</v>
+        <v>0.9619239288483692</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -2849,10 +2849,10 @@
         <v>7.300099999999984</v>
       </c>
       <c r="B223">
-        <v>0.9390198551896907</v>
+        <v>0.9844683081932182</v>
       </c>
       <c r="C223">
-        <v>0.9999771035003092</v>
+        <v>0.9618212895704268</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -2860,10 +2860,10 @@
         <v>7.333433333333318</v>
       </c>
       <c r="B224">
-        <v>0.938907160064793</v>
+        <v>0.9845846528336095</v>
       </c>
       <c r="C224">
-        <v>0.999963279107219</v>
+        <v>0.9617193490372126</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -2871,10 +2871,10 @@
         <v>7.366766666666651</v>
       </c>
       <c r="B225">
-        <v>0.9387637568519617</v>
+        <v>0.9847246213668619</v>
       </c>
       <c r="C225">
-        <v>0.9999532130696811</v>
+        <v>0.9616180454639124</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -2882,10 +2882,10 @@
         <v>7.400099999999984</v>
       </c>
       <c r="B226">
-        <v>0.9386052906405649</v>
+        <v>0.9848773253622758</v>
       </c>
       <c r="C226">
-        <v>0.9999476816202237</v>
+        <v>0.9615173230002231</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -2893,10 +2893,10 @@
         <v>7.433433333333317</v>
       </c>
       <c r="B227">
-        <v>0.9384482218368398</v>
+        <v>0.9850313893566015</v>
       </c>
       <c r="C227">
-        <v>0.9999470142248744</v>
+        <v>0.9614171359139881</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -2904,10 +2904,10 @@
         <v>7.466766666666651</v>
       </c>
       <c r="B228">
-        <v>0.9383082790028866</v>
+        <v>0.9851759479209984</v>
       </c>
       <c r="C228">
-        <v>0.9999510817385312</v>
+        <v>0.961317450169688</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -2915,10 +2915,10 @@
         <v>7.500099999999984</v>
       </c>
       <c r="B229">
-        <v>0.9381990009155562</v>
+        <v>0.9853013447455956</v>
       </c>
       <c r="C229">
-        <v>0.9999593274730176</v>
+        <v>0.961218243455964</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -2926,10 +2926,10 @@
         <v>7.533433333333317</v>
       </c>
       <c r="B230">
-        <v>0.9381305190214095</v>
+        <v>0.9853997007327268</v>
       </c>
       <c r="C230">
-        <v>0.9999708361835308</v>
+        <v>0.9611195033309005</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -2937,10 +2937,10 @@
         <v>7.56676666666665</v>
       </c>
       <c r="B231">
-        <v>0.9381091992635854</v>
+        <v>0.9854652174585067</v>
       </c>
       <c r="C231">
-        <v>0.9999844457188288</v>
+        <v>0.9610212243778918</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -2948,10 +2948,10 @@
         <v>7.600099999999983</v>
       </c>
       <c r="B232">
-        <v>0.9381350364277861</v>
+        <v>0.985494354718787</v>
       </c>
       <c r="C232">
-        <v>0.999998806762537</v>
+        <v>0.9609234069871183</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -2959,10 +2959,10 @@
         <v>7.633433333333317</v>
       </c>
       <c r="B233">
-        <v>0.9382053708648351</v>
+        <v>0.9854859303981818</v>
       </c>
       <c r="C233">
-        <v>1.00001258775136</v>
+        <v>0.9608260575588392</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -2970,10 +2970,10 @@
         <v>7.66676666666665</v>
       </c>
       <c r="B234">
-        <v>0.9383131045507448</v>
+        <v>0.9854411684159946</v>
       </c>
       <c r="C234">
-        <v>1.000024602561658</v>
+        <v>0.9607291900969464</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -2981,10 +2981,10 @@
         <v>7.700099999999983</v>
       </c>
       <c r="B235">
-        <v>0.9384474170673087</v>
+        <v>0.9853636578213969</v>
       </c>
       <c r="C235">
-        <v>1.000033811897853</v>
+        <v>0.9606328283006947</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -2992,10 +2992,10 @@
         <v>7.733433333333316</v>
       </c>
       <c r="B236">
-        <v>0.938595739883006</v>
+        <v>0.9852592112271963</v>
       </c>
       <c r="C236">
-        <v>1.000039482058155</v>
+        <v>0.9605370072471797</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -3003,10 +3003,10 @@
         <v>7.766766666666649</v>
       </c>
       <c r="B237">
-        <v>0.93874474847111</v>
+        <v>0.9851354992229395</v>
       </c>
       <c r="C237">
-        <v>1.000041246397909</v>
+        <v>0.9604417727515089</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -3014,10 +3014,10 @@
         <v>7.800099999999983</v>
       </c>
       <c r="B238">
-        <v>0.938881609994821</v>
+        <v>0.9850015119703456</v>
       </c>
       <c r="C238">
-        <v>1.000039102028997</v>
+        <v>0.9603471794058361</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -3025,10 +3025,10 @@
         <v>7.833433333333316</v>
       </c>
       <c r="B239">
-        <v>0.9389951068029939</v>
+        <v>0.9848668299825044</v>
       </c>
       <c r="C239">
-        <v>1.000033401557209</v>
+        <v>0.9602532859138108</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -3036,10 +3036,10 @@
         <v>7.866766666666649</v>
       </c>
       <c r="B240">
-        <v>0.9390765525467423</v>
+        <v>0.9847408574913891</v>
       </c>
       <c r="C240">
-        <v>1.000024808107251</v>
+        <v>0.9601601493457527</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -3047,10 +3047,10 @@
         <v>7.900099999999982</v>
       </c>
       <c r="B241">
-        <v>0.9391204417941311</v>
+        <v>0.9846319990892763</v>
       </c>
       <c r="C241">
-        <v>1.000014223292081</v>
+        <v>0.9600678201571061</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -3058,10 +3058,10 @@
         <v>7.933433333333316</v>
       </c>
       <c r="B242">
-        <v>0.939124799732862</v>
+        <v>0.9845470463648484</v>
       </c>
       <c r="C242">
-        <v>1.000002695867761</v>
+        <v>0.9599763371419877</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -3069,10 +3069,10 @@
         <v>7.966766666666649</v>
       </c>
       <c r="B243">
-        <v>0.9390912964892262</v>
+        <v>0.9844907369972681</v>
       </c>
       <c r="C243">
-        <v>0.9999913206938725</v>
+        <v>0.9598857247894894</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -3080,10 +3080,10 @@
         <v>8.000099999999982</v>
       </c>
       <c r="B244">
-        <v>0.9390248631670787</v>
+        <v>0.9844655534126544</v>
       </c>
       <c r="C244">
-        <v>0.9999811397944088</v>
+        <v>0.9597959920337591</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -3091,10 +3091,10 @@
         <v>8.033433333333315</v>
       </c>
       <c r="B245">
-        <v>0.9389325967434371</v>
+        <v>0.9844717345080518</v>
       </c>
       <c r="C245">
-        <v>0.9999730259837358</v>
+        <v>0.9597071319368708</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -3102,10 +3102,10 @@
         <v>8.066766666666648</v>
       </c>
       <c r="B246">
-        <v>0.9388248586948955</v>
+        <v>0.984507451125836</v>
       </c>
       <c r="C246">
-        <v>0.999967647466159</v>
+        <v>0.9596191215914357</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -3113,10 +3113,10 @@
         <v>8.100099999999982</v>
       </c>
       <c r="B247">
-        <v>0.938712106804188</v>
+        <v>0.9845690813601913</v>
       </c>
       <c r="C247">
-        <v>0.9999654049762184</v>
+        <v>0.9595319224194075</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -3124,10 +3124,10 @@
         <v>8.133433333333315</v>
       </c>
       <c r="B248">
-        <v>0.9386050914026178</v>
+        <v>0.9846515930250765</v>
       </c>
       <c r="C248">
-        <v>0.9999663706380699</v>
+        <v>0.9594454783495887</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -3135,10 +3135,10 @@
         <v>8.166766666666648</v>
       </c>
       <c r="B249">
-        <v>0.9385136148194512</v>
+        <v>0.9847488993753823</v>
       </c>
       <c r="C249">
-        <v>0.9999703299464545</v>
+        <v>0.959359719086612</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -3146,10 +3146,10 @@
         <v>8.200099999999981</v>
       </c>
       <c r="B250">
-        <v>0.9384456435447933</v>
+        <v>0.9848542805206371</v>
       </c>
       <c r="C250">
-        <v>0.9999768061008466</v>
+        <v>0.9592745636121915</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -3157,10 +3157,10 @@
         <v>8.233433333333315</v>
       </c>
       <c r="B251">
-        <v>0.9384066251271668</v>
+        <v>0.9849608976330303</v>
       </c>
       <c r="C251">
-        <v>0.9999851108694622</v>
+        <v>0.9591899228971024</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -3168,10 +3168,10 @@
         <v>8.266766666666648</v>
       </c>
       <c r="B252">
-        <v>0.9383993028167894</v>
+        <v>0.9850622271312778</v>
       </c>
       <c r="C252">
-        <v>0.9999944234186134</v>
+        <v>0.9591057088989319</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -3179,10 +3179,10 @@
         <v>8.300099999999981</v>
       </c>
       <c r="B253">
-        <v>0.9384225019884193</v>
+        <v>0.9851525126255919</v>
       </c>
       <c r="C253">
-        <v>1.000003841246429</v>
+        <v>0.9590218430627278</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -3190,10 +3190,10 @@
         <v>8.333433333333314</v>
       </c>
       <c r="B254">
-        <v>0.938473199197402</v>
+        <v>0.9852271197802349</v>
       </c>
       <c r="C254">
-        <v>1.000012506199997</v>
+        <v>0.958938264098431</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -3201,10 +3201,10 @@
         <v>8.366766666666647</v>
       </c>
       <c r="B255">
-        <v>0.9385458058376402</v>
+        <v>0.9852827505244849</v>
       </c>
       <c r="C255">
-        <v>1.000019688469746</v>
+        <v>0.9588549338195421</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -3212,10 +3212,10 @@
         <v>8.40009999999998</v>
       </c>
       <c r="B256">
-        <v>0.938632376031871</v>
+        <v>0.9853174879348359</v>
       </c>
       <c r="C256">
-        <v>1.000024780561854</v>
+        <v>0.9587718397515613</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -3223,10 +3223,10 @@
         <v>8.433433333333314</v>
       </c>
       <c r="B257">
-        <v>0.9387243900009943</v>
+        <v>0.9853306888174638</v>
       </c>
       <c r="C257">
-        <v>1.000027392082727</v>
+        <v>0.9586889950142742</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -3234,10 +3234,10 @@
         <v>8.466766666666647</v>
       </c>
       <c r="B258">
-        <v>0.9388131002596014</v>
+        <v>0.9853227638668448</v>
       </c>
       <c r="C258">
-        <v>1.000027393865794</v>
+        <v>0.9586064345544374</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -3245,10 +3245,10 @@
         <v>8.50009999999998</v>
       </c>
       <c r="B259">
-        <v>0.9388904026167314</v>
+        <v>0.985294940719952</v>
       </c>
       <c r="C259">
-        <v>1.000024893076239</v>
+        <v>0.9585242100573179</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -3256,10 +3256,10 @@
         <v>8.533433333333313</v>
       </c>
       <c r="B260">
-        <v>0.9389495383879372</v>
+        <v>0.9852490686881226</v>
       </c>
       <c r="C260">
-        <v>1.000020217911318</v>
+        <v>0.9584423854266637</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -3267,10 +3267,10 @@
         <v>8.566766666666647</v>
       </c>
       <c r="B261">
-        <v>0.9389856379855617</v>
+        <v>0.9851875176330814</v>
       </c>
       <c r="C261">
-        <v>1.0000138829197</v>
+        <v>0.958361032040446</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -3278,10 +3278,10 @@
         <v>8.60009999999998</v>
       </c>
       <c r="B262">
-        <v>0.9389958967063063</v>
+        <v>0.9851131674437112</v>
       </c>
       <c r="C262">
-        <v>1.000006529847689</v>
+        <v>0.9582802248015397</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -3289,10 +3289,10 @@
         <v>8.633433333333313</v>
       </c>
       <c r="B263">
-        <v>0.9389805612222301</v>
+        <v>0.9850294598752529</v>
       </c>
       <c r="C263">
-        <v>0.9999988836453102</v>
+        <v>0.9582000395574178</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -3300,10 +3300,10 @@
         <v>8.666766666666646</v>
       </c>
       <c r="B264">
-        <v>0.938941402719165</v>
+        <v>0.9849404131700865</v>
       </c>
       <c r="C264">
-        <v>0.9999916564239757</v>
+        <v>0.9581205491977391</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -3311,10 +3311,10 @@
         <v>8.70009999999998</v>
       </c>
       <c r="B265">
-        <v>0.9388823323869772</v>
+        <v>0.9848505736635306</v>
       </c>
       <c r="C265">
-        <v>0.9999854764051488</v>
+        <v>0.9580418185227787</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -3322,10 +3322,10 @@
         <v>8.733433333333313</v>
       </c>
       <c r="B266">
-        <v>0.9388093744316958</v>
+        <v>0.9847648396845973</v>
       </c>
       <c r="C266">
-        <v>0.9999808777234683</v>
+        <v>0.9579638991370403</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -3333,10 +3333,10 @@
         <v>8.766766666666646</v>
       </c>
       <c r="B267">
-        <v>0.9387292266833767</v>
+        <v>0.984688172782178</v>
       </c>
       <c r="C267">
-        <v>0.999978227447859</v>
+        <v>0.9578868232204555</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -3344,10 +3344,10 @@
         <v>8.80009999999998</v>
       </c>
       <c r="B268">
-        <v>0.9386490446473309</v>
+        <v>0.9846252381069608</v>
       </c>
       <c r="C268">
-        <v>0.9999776868508444</v>
+        <v>0.9578105983022045</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -3355,10 +3355,10 @@
         <v>8.833433333333312</v>
       </c>
       <c r="B269">
-        <v>0.9385757021972642</v>
+        <v>0.9845800447017601</v>
       </c>
       <c r="C269">
-        <v>0.9999792216335253</v>
+        <v>0.9577352044378988</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -3366,10 +3366,10 @@
         <v>8.866766666666646</v>
       </c>
       <c r="B270">
-        <v>0.9385151646550238</v>
+        <v>0.9845556112571101</v>
       </c>
       <c r="C270">
-        <v>0.9999826111579976</v>
+        <v>0.9576605940688674</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -3377,10 +3377,10 @@
         <v>8.900099999999979</v>
       </c>
       <c r="B271">
-        <v>0.9384719685606894</v>
+        <v>0.9845537947926495</v>
       </c>
       <c r="C271">
-        <v>0.9999874738724571</v>
+        <v>0.9575866980248049</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -3388,10 +3388,10 @@
         <v>8.933433333333312</v>
       </c>
       <c r="B272">
-        <v>0.938448853347581</v>
+        <v>0.9845751554993826</v>
       </c>
       <c r="C272">
-        <v>0.9999933091255875</v>
+        <v>0.9575134309455007</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -3399,10 +3399,10 @@
         <v>8.966766666666645</v>
       </c>
       <c r="B273">
-        <v>0.9384466579337045</v>
+        <v>0.9846189319825536</v>
       </c>
       <c r="C273">
-        <v>0.9999995505398368</v>
+        <v>0.9574406998581878</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -3410,10 +3410,10 @@
         <v>9.000099999999978</v>
       </c>
       <c r="B274">
-        <v>0.9384639001825368</v>
+        <v>0.9846830827635729</v>
       </c>
       <c r="C274">
-        <v>1.000005606206468</v>
+        <v>0.9573684152014523</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -3421,10 +3421,10 @@
         <v>9.033433333333312</v>
       </c>
       <c r="B275">
-        <v>0.9384977871171858</v>
+        <v>0.9847643499879049</v>
       </c>
       <c r="C275">
-        <v>1.000010935154303</v>
+        <v>0.9572964965750203</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -3432,10 +3432,10 @@
         <v>9.066766666666645</v>
       </c>
       <c r="B276">
-        <v>0.9385439260079129</v>
+        <v>0.9848583575503641</v>
       </c>
       <c r="C276">
-        <v>1.000015092128569</v>
+        <v>0.9572248780043237</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -3443,10 +3443,10 @@
         <v>9.100099999999978</v>
       </c>
       <c r="B277">
-        <v>0.9385969691461328</v>
+        <v>0.9849597586988577</v>
       </c>
       <c r="C277">
-        <v>1.000017742167433</v>
+        <v>0.9571535105426074</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -3454,10 +3454,10 @@
         <v>9.133433333333311</v>
       </c>
       <c r="B278">
-        <v>0.9386511485845989</v>
+        <v>0.9850624557091032</v>
       </c>
       <c r="C278">
-        <v>1.000018703767456</v>
+        <v>0.9570823629887134</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -3465,10 +3465,10 @@
         <v>9.166766666666645</v>
       </c>
       <c r="B279">
-        <v>0.9387008199799188</v>
+        <v>0.9851599450125336</v>
       </c>
       <c r="C279">
-        <v>1.000017957124931</v>
+        <v>0.9570114221482803</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -3476,10 +3476,10 @@
         <v>9.200099999999978</v>
       </c>
       <c r="B280">
-        <v>0.9387409682118604</v>
+        <v>0.9852457014060173</v>
       </c>
       <c r="C280">
-        <v>1.000015638980717</v>
+        <v>0.9569406919230516</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -3487,10 +3487,10 @@
         <v>9.233433333333311</v>
       </c>
       <c r="B281">
-        <v>0.9387676321883034</v>
+        <v>0.9853136879394893</v>
       </c>
       <c r="C281">
-        <v>1.000012024015994</v>
+        <v>0.9568701924590625</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -3498,10 +3498,10 @@
         <v>9.266766666666644</v>
       </c>
       <c r="B282">
-        <v>0.9387782164628602</v>
+        <v>0.985358841280675</v>
       </c>
       <c r="C282">
-        <v>1.000007494446455</v>
+        <v>0.956799959453258</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -3509,10 +3509,10 @@
         <v>9.300099999999977</v>
       </c>
       <c r="B283">
-        <v>0.9387716687014718</v>
+        <v>0.9853775057829868</v>
       </c>
       <c r="C283">
-        <v>1.00000250093813</v>
+        <v>0.9567300416286272</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -3520,10 +3520,10 @@
         <v>9.33343333333331</v>
       </c>
       <c r="B284">
-        <v>0.9387485138887786</v>
+        <v>0.9853677529877369</v>
       </c>
       <c r="C284">
-        <v>0.9999975187430431</v>
+        <v>0.9566604970405241</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -3531,10 +3531,10 @@
         <v>9.366766666666644</v>
       </c>
       <c r="B285">
-        <v>0.9387106813486893</v>
+        <v>0.9853295555761431</v>
       </c>
       <c r="C285">
-        <v>0.9999930008220757</v>
+        <v>0.9565913881107544</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -3542,10 +3542,10 @@
         <v>9.400099999999977</v>
       </c>
       <c r="B286">
-        <v>0.9386614655308477</v>
+        <v>0.985264814795662</v>
       </c>
       <c r="C286">
-        <v>0.9999893436425911</v>
+        <v>0.9565227759824816</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -3553,10 +3553,10 @@
         <v>9.43343333333331</v>
       </c>
       <c r="B287">
-        <v>0.9386050277185836</v>
+        <v>0.9851772625575215</v>
       </c>
       <c r="C287">
-        <v>0.9999868515870458</v>
+        <v>0.9564547151327051</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -3564,10 +3564,10 @@
         <v>9.466766666666643</v>
       </c>
       <c r="B288">
-        <v>0.9385460000044478</v>
+        <v>0.9850722654457703</v>
       </c>
       <c r="C288">
-        <v>0.999985705146512</v>
+        <v>0.9563872491788005</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -3575,10 +3575,10 @@
         <v>9.500099999999977</v>
       </c>
       <c r="B289">
-        <v>0.9384890668986258</v>
+        <v>0.9849565478347435</v>
       </c>
       <c r="C289">
-        <v>0.9999859548770579</v>
+        <v>0.956320408491689</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -3586,10 +3586,10 @@
         <v>9.53343333333331</v>
       </c>
       <c r="B290">
-        <v>0.9384385329392564</v>
+        <v>0.9848378336729963</v>
       </c>
       <c r="C290">
-        <v>0.9999875232063214</v>
+        <v>0.9562542097162859</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -3597,10 +3597,10 @@
         <v>9.566766666666643</v>
       </c>
       <c r="B291">
-        <v>0.9383979410611846</v>
+        <v>0.984724394101088</v>
       </c>
       <c r="C291">
-        <v>0.9999902152093871</v>
+        <v>0.9561886567937458</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -3608,10 +3608,10 @@
         <v>9.600099999999976</v>
       </c>
       <c r="B292">
-        <v>0.9383697746694795</v>
+        <v>0.9846244917394482</v>
       </c>
       <c r="C292">
-        <v>0.9999937412671671</v>
+        <v>0.9561237427573748</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -3619,10 +3619,10 @@
         <v>9.63343333333331</v>
       </c>
       <c r="B293">
-        <v>0.9383552695654656</v>
+        <v>0.9845457354146578</v>
       </c>
       <c r="C293">
-        <v>0.9999977473434307</v>
+        <v>0.9560594515400755</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -3630,10 +3630,10 @@
         <v>9.666766666666643</v>
       </c>
       <c r="B294">
-        <v>0.9383543516069764</v>
+        <v>0.9844943948105171</v>
       </c>
       <c r="C294">
-        <v>1.000001850743472</v>
+        <v>0.9559957592868681</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -3641,10 +3641,10 @@
         <v>9.700099999999976</v>
       </c>
       <c r="B295">
-        <v>0.9383656235298324</v>
+        <v>0.9844747592872274</v>
       </c>
       <c r="C295">
-        <v>1.000005670401221</v>
+        <v>0.9559326351038941</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -3652,10 +3652,10 @@
         <v>9.73343333333331</v>
       </c>
       <c r="B296">
-        <v>0.9383867609940386</v>
+        <v>0.9844886436223736</v>
       </c>
       <c r="C296">
-        <v>1.000008872129807</v>
+        <v>0.9558700416091511</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -3663,10 +3663,10 @@
         <v>9.766766666666642</v>
       </c>
       <c r="B297">
-        <v>0.938414562136342</v>
+        <v>0.9845351352814747</v>
       </c>
       <c r="C297">
-        <v>1.000011193998453</v>
+        <v>0.9558079358823248</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -3674,10 +3674,10 @@
         <v>9.800099999999976</v>
       </c>
       <c r="B298">
-        <v>0.9384453427521408</v>
+        <v>0.9846106418446902</v>
       </c>
       <c r="C298">
-        <v>1.000012457414543</v>
+        <v>0.9557462713208281</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -3685,10 +3685,10 @@
         <v>9.833433333333309</v>
       </c>
       <c r="B299">
-        <v>0.9384752947057585</v>
+        <v>0.9847092541024014</v>
       </c>
       <c r="C299">
-        <v>1.000012589229366</v>
+        <v>0.955685000521276</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -3696,10 +3696,10 @@
         <v>9.866766666666642</v>
       </c>
       <c r="B300">
-        <v>0.9385008374325985</v>
+        <v>0.9848232976623961</v>
       </c>
       <c r="C300">
-        <v>1.00001162259798</v>
+        <v>0.955624078603864</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -3707,10 +3707,10 @@
         <v>9.900099999999975</v>
       </c>
       <c r="B301">
-        <v>0.9385189327791816</v>
+        <v>0.984944145861032</v>
       </c>
       <c r="C301">
-        <v>1.000009689487377</v>
+        <v>0.9555634674731751</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -3718,10 +3718,10 @@
         <v>9.933433333333308</v>
       </c>
       <c r="B302">
-        <v>0.9385273369879613</v>
+        <v>0.9850629893515376</v>
       </c>
       <c r="C302">
-        <v>1.000007004750126</v>
+        <v>0.955503136716559</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -3729,10 +3729,10 @@
         <v>9.966766666666642</v>
       </c>
       <c r="B303">
-        <v>0.938524770777619</v>
+        <v>0.9851714960748702</v>
       </c>
       <c r="C303">
-        <v>1.000003843284831</v>
+        <v>0.9554430654616264</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -3740,10 +3740,10 @@
         <v>10.00009999999997</v>
       </c>
       <c r="B304">
-        <v>0.9385109963717866</v>
+        <v>0.9852624188696674</v>
       </c>
       <c r="C304">
-        <v>1.000000512595151</v>
+        <v>0.9553832419753466</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -3751,10 +3751,10 @@
         <v>10.03343333333331</v>
       </c>
       <c r="B305">
-        <v>0.9384868014194704</v>
+        <v>0.9853299882708283</v>
       </c>
       <c r="C305">
-        <v>0.9999973225778563</v>
+        <v>0.9553236617427711</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -3762,10 +3762,10 @@
         <v>10.06676666666664</v>
       </c>
       <c r="B306">
-        <v>0.9384538250680052</v>
+        <v>0.9853701712827835</v>
       </c>
       <c r="C306">
-        <v>0.9999945584151837</v>
+        <v>0.955264326009354</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -3773,10 +3773,10 @@
         <v>10.10009999999997</v>
       </c>
       <c r="B307">
-        <v>0.9384145572641085</v>
+        <v>0.9853808213485677</v>
       </c>
       <c r="C307">
-        <v>0.9999924575594908</v>
+        <v>0.9552052408488417</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -3784,10 +3784,10 @@
         <v>10.13343333333331</v>
       </c>
       <c r="B308">
-        <v>0.9383719040642956</v>
+        <v>0.9853617498624249</v>
       </c>
       <c r="C308">
-        <v>0.9999911860157372</v>
+        <v>0.9551464172035691</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -3795,10 +3795,10 @@
         <v>10.16676666666664</v>
       </c>
       <c r="B309">
-        <v>0.9383289676537455</v>
+        <v>0.9853147269681557</v>
       </c>
       <c r="C309">
-        <v>0.9999908257596883</v>
+        <v>0.9550878717413288</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -3806,10 +3806,10 @@
         <v>10.20009999999997</v>
       </c>
       <c r="B310">
-        <v>0.9382887553230582</v>
+        <v>0.9852433940365077</v>
       </c>
       <c r="C310">
-        <v>0.9999913733230477</v>
+        <v>0.9550296279439218</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -3817,10 +3817,10 @@
         <v>10.23343333333331</v>
       </c>
       <c r="B311">
-        <v>0.9382539081256794</v>
+        <v>0.985153056758697</v>
       </c>
       <c r="C311">
-        <v>0.9999927426347873</v>
+        <v>0.9549717166663234</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -3828,10 +3828,10 @@
         <v>10.26676666666664</v>
       </c>
       <c r="B312">
-        <v>0.9382264727046589</v>
+        <v>0.9850503347288373</v>
       </c>
       <c r="C312">
-        <v>0.9999947761504502</v>
+        <v>0.954914175527293</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -3839,10 +3839,10 @@
         <v>10.30009999999997</v>
       </c>
       <c r="B313">
-        <v>0.9382077364875536</v>
+        <v>0.9849426695238152</v>
       </c>
       <c r="C313">
-        <v>0.9999972620960077</v>
+        <v>0.9548570468557236</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -3850,10 +3850,10 @@
         <v>10.33343333333331</v>
       </c>
       <c r="B314">
-        <v>0.9381981395316075</v>
+        <v>0.9848377203003473</v>
       </c>
       <c r="C314">
-        <v>0.9999999559497807</v>
+        <v>0.9548003743846498</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -3861,10 +3861,10 @@
         <v>10.36676666666664</v>
       </c>
       <c r="B315">
-        <v>0.9381972350926512</v>
+        <v>0.9847427634697163</v>
       </c>
       <c r="C315">
-        <v>1.000002604009188</v>
+        <v>0.9547441990900468</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -3872,10 +3872,10 @@
         <v>10.40009999999997</v>
       </c>
       <c r="B316">
-        <v>0.938203854837737</v>
+        <v>0.9846640627861031</v>
       </c>
       <c r="C316">
-        <v>1.000004965392794</v>
+        <v>0.9546885559481316</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -3883,10 +3883,10 @@
         <v>10.43343333333331</v>
       </c>
       <c r="B317">
-        <v>0.9382161825866481</v>
+        <v>0.9846064320567358</v>
       </c>
       <c r="C317">
-        <v>1.000006838057879</v>
+        <v>0.9546334702273241</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -3894,10 +3894,10 @@
         <v>10.46676666666664</v>
       </c>
       <c r="B318">
-        <v>0.9382319474013318</v>
+        <v>0.9845729346505843</v>
       </c>
       <c r="C318">
-        <v>1.000008072621043</v>
+        <v>0.9545789558190525</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -3905,10 +3905,10 @@
         <v>10.50009999999997</v>
       </c>
       <c r="B319">
-        <v>0.9382486591521382</v>
+        <v>0.984564774456018</v>
       </c>
       <c r="C319">
-        <v>1.000008580418934</v>
+        <v>0.9545250143467238</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -3916,10 +3916,10 @@
         <v>10.53343333333331</v>
       </c>
       <c r="B320">
-        <v>0.9382638454152307</v>
+        <v>0.9845813519646722</v>
       </c>
       <c r="C320">
-        <v>1.000008343747792</v>
+        <v>0.9544716355716986</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -3927,10 +3927,10 @@
         <v>10.56676666666664</v>
       </c>
       <c r="B321">
-        <v>0.9382752753498567</v>
+        <v>0.9846204593503597</v>
       </c>
       <c r="C321">
-        <v>1.00000741351755</v>
+        <v>0.9544187956271771</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -3938,10 +3938,10 @@
         <v>10.60009999999997</v>
       </c>
       <c r="B322">
-        <v>0.9382811520741335</v>
+        <v>0.9846785488960829</v>
       </c>
       <c r="C322">
-        <v>1.000005901801095</v>
+        <v>0.9543664588410563</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -3949,10 +3949,10 @@
         <v>10.63343333333331</v>
       </c>
       <c r="B323">
-        <v>0.9382802577220759</v>
+        <v>0.9847510580513728</v>
       </c>
       <c r="C323">
-        <v>1.000003969207371</v>
+        <v>0.954314579746127</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -3960,10 +3960,10 @@
         <v>10.66676666666664</v>
       </c>
       <c r="B324">
-        <v>0.938272040444277</v>
+        <v>0.9848327644796491</v>
       </c>
       <c r="C324">
-        <v>1.00000180833099</v>
+        <v>0.9542631024741511</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -3971,10 +3971,10 @@
         <v>10.70009999999997</v>
       </c>
       <c r="B325">
-        <v>0.938256638145789</v>
+        <v>0.9849181607336505</v>
       </c>
       <c r="C325">
-        <v>0.9999996249351336</v>
+        <v>0.9542119644854039</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -3982,10 +3982,10 @@
         <v>10.73343333333331</v>
       </c>
       <c r="B326">
-        <v>0.9382348375737541</v>
+        <v>0.9850018041080202</v>
       </c>
       <c r="C326">
-        <v>0.9999976176509789</v>
+        <v>0.954161099814692</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -3993,10 +3993,10 @@
         <v>10.76676666666664</v>
       </c>
       <c r="B327">
-        <v>0.9382079512677748</v>
+        <v>0.9850787086988803</v>
       </c>
       <c r="C327">
-        <v>0.9999959626020204</v>
+        <v>0.9541104451325656</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -4004,10 +4004,10 @@
         <v>10.80009999999997</v>
       </c>
       <c r="B328">
-        <v>0.9381777733986836</v>
+        <v>0.9851446331426214</v>
       </c>
       <c r="C328">
-        <v>0.9999947979505914</v>
+        <v>0.9540599465126043</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -4015,10 +4015,10 @@
         <v>10.83343333333331</v>
       </c>
       <c r="B329">
-        <v>0.9381462963367402</v>
+        <v>0.9851963203714176</v>
       </c>
       <c r="C329">
-        <v>0.9999942096184165</v>
+        <v>0.9540095637882975</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -4026,10 +4026,10 @@
         <v>10.86676666666664</v>
       </c>
       <c r="B330">
-        <v>0.9381155585235698</v>
+        <v>0.9852316213162959</v>
       </c>
       <c r="C330">
-        <v>0.9999942274054322</v>
+        <v>0.953959274335416</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -4037,10 +4037,10 @@
         <v>10.90009999999997</v>
       </c>
       <c r="B331">
-        <v>0.938087455836662</v>
+        <v>0.9852495048425058</v>
       </c>
       <c r="C331">
-        <v>0.9999948252233565</v>
+        <v>0.9539090753838562</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -4048,10 +4048,10 @@
         <v>10.9334333333333</v>
       </c>
       <c r="B332">
-        <v>0.9380635740699655</v>
+        <v>0.9852499493110486</v>
       </c>
       <c r="C332">
-        <v>0.9999959251392017</v>
+        <v>0.9538589828088891</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -4059,10 +4059,10 @@
         <v>10.96676666666664</v>
       </c>
       <c r="B333">
-        <v>0.9380450559453704</v>
+        <v>0.9852337802188696</v>
       </c>
       <c r="C333">
-        <v>0.9999974065825512</v>
+        <v>0.953809028311527</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -4070,10 +4070,10 @@
         <v>11.00009999999997</v>
       </c>
       <c r="B334">
-        <v>0.9380325285389076</v>
+        <v>0.9852024824950066</v>
       </c>
       <c r="C334">
-        <v>0.9999991204203149</v>
+        <v>0.9537592566795875</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -4081,10 +4081,10 @@
         <v>11.0334333333333</v>
       </c>
       <c r="B335">
-        <v>0.9380259825493511</v>
+        <v>0.9851580434407942</v>
       </c>
       <c r="C335">
-        <v>1.000000897702958</v>
+        <v>0.9537097216318244</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -4092,10 +4092,10 @@
         <v>11.06676666666664</v>
       </c>
       <c r="B336">
-        <v>0.9380249606468365</v>
+        <v>0.985102851109577</v>
       </c>
       <c r="C336">
-        <v>1.000002573810668</v>
+        <v>0.9536604821510704</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -4103,10 +4103,10 @@
         <v>11.10009999999997</v>
       </c>
       <c r="B337">
-        <v>0.9380284901231039</v>
+        <v>0.9850396438428023</v>
       </c>
       <c r="C337">
-        <v>1.00000400348315</v>
+        <v>0.953611598920593</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -4114,10 +4114,10 @@
         <v>11.1334333333333</v>
       </c>
       <c r="B338">
-        <v>0.9380352270262731</v>
+        <v>0.9849715006825565</v>
       </c>
       <c r="C338">
-        <v>1.000005064619334</v>
+        <v>0.9535631319594384</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -4125,10 +4125,10 @@
         <v>11.16676666666664</v>
       </c>
       <c r="B339">
-        <v>0.9380435957201666</v>
+        <v>0.9849017945857502</v>
       </c>
       <c r="C339">
-        <v>1.000005674476736</v>
+        <v>0.9535151368629847</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -4136,10 +4136,10 @@
         <v>11.20009999999997</v>
       </c>
       <c r="B340">
-        <v>0.9380519419230577</v>
+        <v>0.9848341192736164</v>
       </c>
       <c r="C340">
-        <v>1.000005794961749</v>
+        <v>0.9534676603483222</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -4147,10 +4147,10 @@
         <v>11.2334333333333</v>
       </c>
       <c r="B341">
-        <v>0.9380586865122975</v>
+        <v>0.9847721374679855</v>
       </c>
       <c r="C341">
-        <v>1.000005434069817</v>
+        <v>0.953420736693543</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -4158,10 +4158,10 @@
         <v>11.26676666666664</v>
       </c>
       <c r="B342">
-        <v>0.9380624659267112</v>
+        <v>0.984719370666105</v>
       </c>
       <c r="C342">
-        <v>1.0000046433008</v>
+        <v>0.9533743834755682</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -4169,10 +4169,10 @@
         <v>11.30009999999997</v>
       </c>
       <c r="B343">
-        <v>0.9380622471552721</v>
+        <v>0.9846789624099737</v>
       </c>
       <c r="C343">
-        <v>1.000003511248803</v>
+        <v>0.9533285987439635</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -4180,10 +4180,10 @@
         <v>11.3334333333333</v>
       </c>
       <c r="B344">
-        <v>0.9380574081141599</v>
+        <v>0.9846534271746155</v>
       </c>
       <c r="C344">
-        <v>1.000002154069636</v>
+        <v>0.9532833588024043</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -4191,10 +4191,10 @@
         <v>11.36676666666664</v>
       </c>
       <c r="B345">
-        <v>0.9380477776902093</v>
+        <v>0.9846444951368847</v>
       </c>
       <c r="C345">
-        <v>1.000000703809055</v>
+        <v>0.953238620722325</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -4202,10 +4202,10 @@
         <v>11.40009999999997</v>
       </c>
       <c r="B346">
-        <v>0.9380336335204569</v>
+        <v>0.9846529731951887</v>
       </c>
       <c r="C346">
-        <v>0.9999992957445694</v>
+        <v>0.9531943267286047</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -4213,10 +4213,10 @@
         <v>11.4334333333333</v>
       </c>
       <c r="B347">
-        <v>0.9380156593446004</v>
+        <v>0.9846787057771386</v>
       </c>
       <c r="C347">
-        <v>0.999998055929953</v>
+        <v>0.9531504090801353</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -4224,10 +4224,10 @@
         <v>11.46676666666664</v>
       </c>
       <c r="B348">
-        <v>0.9379948672727964</v>
+        <v>0.9847205704270958</v>
       </c>
       <c r="C348">
-        <v>0.9999970900737866</v>
+        <v>0.9531067953638093</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -4235,10 +4235,10 @@
         <v>11.50009999999997</v>
       </c>
       <c r="B349">
-        <v>0.9379724571605621</v>
+        <v>0.9847765360201954</v>
       </c>
       <c r="C349">
-        <v>0.999996472841095</v>
+        <v>0.9530634163671967</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -4246,10 +4246,10 @@
         <v>11.5334333333333</v>
       </c>
       <c r="B350">
-        <v>0.9379498308704677</v>
+        <v>0.9848437235145117</v>
       </c>
       <c r="C350">
-        <v>0.9999962487331197</v>
+        <v>0.9530202128276942</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -4257,10 +4257,10 @@
         <v>11.56676666666664</v>
       </c>
       <c r="B351">
-        <v>0.937928285806106</v>
+        <v>0.9849184948380008</v>
       </c>
       <c r="C351">
-        <v>0.9999964235303798</v>
+        <v>0.9529771368351054</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -4268,10 +4268,10 @@
         <v>11.60009999999997</v>
       </c>
       <c r="B352">
-        <v>0.937909033969092</v>
+        <v>0.984996605774881</v>
       </c>
       <c r="C352">
-        <v>0.999996963930361</v>
+        <v>0.95293415525896</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -4279,10 +4279,10 @@
         <v>11.6334333333333</v>
       </c>
       <c r="B353">
-        <v>0.9378929149580701</v>
+        <v>0.9850733568705157</v>
       </c>
       <c r="C353">
-        <v>0.9999978023413327</v>
+        <v>0.952891249510466</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -4290,10 +4290,10 @@
         <v>11.66676666666664</v>
       </c>
       <c r="B354">
-        <v>0.9378805814319991</v>
+        <v>0.9851438692287786</v>
       </c>
       <c r="C354">
-        <v>0.9999988493025865</v>
+        <v>0.9528484148429027</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -4301,10 +4301,10 @@
         <v>11.70009999999997</v>
       </c>
       <c r="B355">
-        <v>0.9378722837059923</v>
+        <v>0.9852033934858319</v>
       </c>
       <c r="C355">
-        <v>1.000000004721529</v>
+        <v>0.9528056609477159</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -4312,10 +4312,10 @@
         <v>11.7334333333333</v>
       </c>
       <c r="B356">
-        <v>0.937867900145492</v>
+        <v>0.9852476638456256</v>
       </c>
       <c r="C356">
-        <v>1.000001157672649</v>
+        <v>0.952763010494711</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -4323,10 +4323,10 @@
         <v>11.76676666666664</v>
       </c>
       <c r="B357">
-        <v>0.9378669649921969</v>
+        <v>0.985273251276144</v>
       </c>
       <c r="C357">
-        <v>1.000002202380562</v>
+        <v>0.9527204975467448</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -4334,10 +4334,10 @@
         <v>11.80009999999997</v>
       </c>
       <c r="B358">
-        <v>0.937868724660722</v>
+        <v>0.9852778702558501</v>
       </c>
       <c r="C358">
-        <v>1.000003047457008</v>
+        <v>0.9526781652230882</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -4345,10 +4345,10 @@
         <v>11.8334333333333</v>
       </c>
       <c r="B359">
-        <v>0.9378722182197505</v>
+        <v>0.9852606000853581</v>
       </c>
       <c r="C359">
-        <v>1.000003623355196</v>
+        <v>0.9526360624486905</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -4356,10 +4356,10 @@
         <v>11.86676666666663</v>
       </c>
       <c r="B360">
-        <v>0.9378763734025076</v>
+        <v>0.9852219979705218</v>
       </c>
       <c r="C360">
-        <v>1.00000388778439</v>
+        <v>0.9525942399427841</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -4367,10 +4367,10 @@
         <v>11.90009999999997</v>
       </c>
       <c r="B361">
-        <v>0.9378801087360742</v>
+        <v>0.9851641001481805</v>
       </c>
       <c r="C361">
-        <v>1.000003828470556</v>
+        <v>0.9525527459081197</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -4378,10 +4378,10 @@
         <v>11.9334333333333</v>
       </c>
       <c r="B362">
-        <v>0.937882432236468</v>
+        <v>0.9850903218373925</v>
       </c>
       <c r="C362">
-        <v>1.00000346308384</v>
+        <v>0.9525116220629571</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -4389,10 +4389,10 @@
         <v>11.96676666666663</v>
       </c>
       <c r="B363">
-        <v>0.9378825278853479</v>
+        <v>0.9850052720930432</v>
       </c>
       <c r="C363">
-        <v>1.000002836445747</v>
+        <v>0.9524709006309464</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -4400,10 +4400,10 @@
         <v>12.00009999999997</v>
       </c>
       <c r="B364">
-        <v>0.9378798226110456</v>
+        <v>0.9849144960233572</v>
       </c>
       <c r="C364">
-        <v>1.000002015375707</v>
+        <v>0.9524306026770882</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -4411,10 +4411,10 @@
         <v>12.0334333333333</v>
       </c>
       <c r="B365">
-        <v>0.937874028565468</v>
+        <v>0.9848241493765447</v>
       </c>
       <c r="C365">
-        <v>1.000001081738099</v>
+        <v>0.9523907378376357</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -4422,10 +4422,10 @@
         <v>12.06676666666663</v>
       </c>
       <c r="B366">
-        <v>0.9378651579096343</v>
+        <v>0.9847406064460738</v>
       </c>
       <c r="C366">
-        <v>1.00000012439329</v>
+        <v>0.9523513051623175</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -4433,10 +4433,10 @@
         <v>12.10009999999997</v>
       </c>
       <c r="B367">
-        <v>0.937853495293431</v>
+        <v>0.9846700072734172</v>
       </c>
       <c r="C367">
-        <v>0.9999992220897603</v>
+        <v>0.952312294582606</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -4444,10 +4444,10 @@
         <v>12.1334333333333</v>
       </c>
       <c r="B368">
-        <v>0.9378396192994423</v>
+        <v>0.9846177652995148</v>
       </c>
       <c r="C368">
-        <v>0.9999984744548529</v>
+        <v>0.9522736885042011</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -4455,10 +4455,10 @@
         <v>12.16676666666663</v>
       </c>
       <c r="B369">
-        <v>0.9378242202795712</v>
+        <v>0.9845880774399386</v>
       </c>
       <c r="C369">
-        <v>0.9999979341671318</v>
+        <v>0.9522354631886791</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -4466,10 +4466,10 @@
         <v>12.20009999999997</v>
       </c>
       <c r="B370">
-        <v>0.9378081940210461</v>
+        <v>0.9845834966612977</v>
       </c>
       <c r="C370">
-        <v>0.9999976259154431</v>
+        <v>0.9521975898611831</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -4477,10 +4477,10 @@
         <v>12.2334333333333</v>
       </c>
       <c r="B371">
-        <v>0.9377924168424008</v>
+        <v>0.9846046337558969</v>
       </c>
       <c r="C371">
-        <v>0.9999975863234105</v>
+        <v>0.952160035736649</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -4488,10 +4488,10 @@
         <v>12.26676666666663</v>
       </c>
       <c r="B372">
-        <v>0.9377768493876414</v>
+        <v>0.9846500447452594</v>
       </c>
       <c r="C372">
-        <v>0.999997819082147</v>
+        <v>0.9521227652784967</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -4499,10 +4499,10 @@
         <v>12.30009999999997</v>
       </c>
       <c r="B373">
-        <v>0.9377640997913482</v>
+        <v>0.9847163335657093</v>
       </c>
       <c r="C373">
-        <v>0.9999982553412017</v>
+        <v>0.9520857419300727</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -4510,10 +4510,10 @@
         <v>12.3334333333333</v>
       </c>
       <c r="B374">
-        <v>0.9377537034774598</v>
+        <v>0.9847984627172633</v>
       </c>
       <c r="C374">
-        <v>0.9999988406485998</v>
+        <v>0.9520489303210286</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -4521,10 +4521,10 @@
         <v>12.36676666666663</v>
       </c>
       <c r="B375">
-        <v>0.9377459907548941</v>
+        <v>0.98489022757746</v>
       </c>
       <c r="C375">
-        <v>0.9999995548456042</v>
+        <v>0.9520122986624613</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -4532,10 +4532,10 @@
         <v>12.40009999999997</v>
       </c>
       <c r="B376">
-        <v>0.9377410088632818</v>
+        <v>0.984984823653059</v>
       </c>
       <c r="C376">
-        <v>1.000000319605118</v>
+        <v>0.9519758208523041</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -4543,10 +4543,10 @@
         <v>12.4334333333333</v>
       </c>
       <c r="B377">
-        <v>0.9377385642400028</v>
+        <v>0.985075427407445</v>
       </c>
       <c r="C377">
-        <v>1.000001060178137</v>
+        <v>0.9519394778214904</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -4554,10 +4554,10 @@
         <v>12.46676666666663</v>
       </c>
       <c r="B378">
-        <v>0.9377376071302875</v>
+        <v>0.9851557217957814</v>
       </c>
       <c r="C378">
-        <v>1.000001747061406</v>
+        <v>0.9519032578707038</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -4565,10 +4565,10 @@
         <v>12.50009999999997</v>
       </c>
       <c r="B379">
-        <v>0.9377385780841322</v>
+        <v>0.9852203221816784</v>
       </c>
       <c r="C379">
-        <v>1.000002257873498</v>
+        <v>0.95186715608327</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -4576,10 +4576,10 @@
         <v>12.5334333333333</v>
       </c>
       <c r="B380">
-        <v>0.937740448968023</v>
+        <v>0.9852650873007549</v>
       </c>
       <c r="C380">
-        <v>1.000002529448704</v>
+        <v>0.9518311732018289</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -4587,10 +4587,10 @@
         <v>12.56676666666663</v>
       </c>
       <c r="B381">
-        <v>0.9377424894844455</v>
+        <v>0.9852873229914876</v>
       </c>
       <c r="C381">
-        <v>1.000002609022738</v>
+        <v>0.9517953144925662</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -4598,10 +4598,10 @@
         <v>12.60009999999997</v>
       </c>
       <c r="B382">
-        <v>0.937743998123978</v>
+        <v>0.9852858964747148</v>
       </c>
       <c r="C382">
-        <v>1.000002480179757</v>
+        <v>0.9517595890375173</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -4609,10 +4609,10 @@
         <v>12.6334333333333</v>
       </c>
       <c r="B383">
-        <v>0.9377454200453904</v>
+        <v>0.9852612750537115</v>
       </c>
       <c r="C383">
-        <v>1.00000211351484</v>
+        <v>0.9517240096367344</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -4620,10 +4620,10 @@
         <v>12.66676666666663</v>
       </c>
       <c r="B384">
-        <v>0.937743950855554</v>
+        <v>0.9852154904615329</v>
       </c>
       <c r="C384">
-        <v>1.000001636680173</v>
+        <v>0.9516885931814629</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -4631,10 +4631,10 @@
         <v>12.70009999999997</v>
       </c>
       <c r="B385">
-        <v>0.9377405575880083</v>
+        <v>0.985152017584291</v>
       </c>
       <c r="C385">
-        <v>1.000001110926273</v>
+        <v>0.9516533611091029</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -4642,10 +4642,10 @@
         <v>12.7334333333333</v>
       </c>
       <c r="B386">
-        <v>0.9377350885444908</v>
+        <v>0.9850755521548116</v>
       </c>
       <c r="C386">
-        <v>1.000000491194178</v>
+        <v>0.9516183394460219</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -4653,10 +4653,10 @@
         <v>12.76676666666663</v>
       </c>
       <c r="B387">
-        <v>0.9377276459180168</v>
+        <v>0.984991680901441</v>
       </c>
       <c r="C387">
-        <v>0.9999998659218673</v>
+        <v>0.9515835580683643</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -4664,10 +4664,10 @@
         <v>12.80009999999996</v>
       </c>
       <c r="B388">
-        <v>0.9377185122317584</v>
+        <v>0.9849064565585824</v>
       </c>
       <c r="C388">
-        <v>0.9999992985591768</v>
+        <v>0.9515490490427125</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -4675,10 +4675,10 @@
         <v>12.8334333333333</v>
       </c>
       <c r="B389">
-        <v>0.9377081218114042</v>
+        <v>0.984825913576648</v>
       </c>
       <c r="C389">
-        <v>0.9999988391678024</v>
+        <v>0.9515148441961868</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -4686,10 +4686,10 @@
         <v>12.86676666666663</v>
       </c>
       <c r="B390">
-        <v>0.9376970156162814</v>
+        <v>0.9847555783983447</v>
       </c>
       <c r="C390">
-        <v>0.9999985253029011</v>
+        <v>0.9514809723359364</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -4697,10 +4697,10 @@
         <v>12.90009999999996</v>
       </c>
       <c r="B391">
-        <v>0.9376857883145098</v>
+        <v>0.9847000343684462</v>
       </c>
       <c r="C391">
-        <v>0.9999983798401944</v>
+        <v>0.9514474566206224</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
@@ -4708,10 +4708,10 @@
         <v>12.9334333333333</v>
       </c>
       <c r="B392">
-        <v>0.9376750323141076</v>
+        <v>0.9846625931191995</v>
       </c>
       <c r="C392">
-        <v>0.9999984095123295</v>
+        <v>0.9514143125076692</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -4719,10 +4719,10 @@
         <v>12.96676666666663</v>
       </c>
       <c r="B393">
-        <v>0.9376652839115208</v>
+        <v>0.9846451044035209</v>
       </c>
       <c r="C393">
-        <v>0.9999986048771331</v>
+        <v>0.9513815464843276</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -4730,10 +4730,10 @@
         <v>13.00009999999996</v>
       </c>
       <c r="B394">
-        <v>0.9376569763875674</v>
+        <v>0.9846479113685979</v>
       </c>
       <c r="C394">
-        <v>0.999998941750756</v>
+        <v>0.951349155542054</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -4741,10 +4741,10 @@
         <v>13.0334333333333</v>
       </c>
       <c r="B395">
-        <v>0.9376504040909314</v>
+        <v>0.9846699357594064</v>
       </c>
       <c r="C395">
-        <v>0.9999993839309976</v>
+        <v>0.9513171271880513</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -4752,10 +4752,10 @@
         <v>13.06676666666663</v>
       </c>
       <c r="B396">
-        <v>0.937645700420934</v>
+        <v>0.9847088633286464</v>
       </c>
       <c r="C396">
-        <v>0.9999998869176593</v>
+        <v>0.951285439781482</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -4763,10 +4763,10 @@
         <v>13.10009999999996</v>
       </c>
       <c r="B397">
-        <v>0.937642831254914</v>
+        <v>0.9847613956238039</v>
       </c>
       <c r="C397">
-        <v>1.000000402255731</v>
+        <v>0.9512540630977058</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -4774,10 +4774,10 @@
         <v>13.1334333333333</v>
       </c>
       <c r="B398">
-        <v>0.9376416038951876</v>
+        <v>0.9848235392312288</v>
       </c>
       <c r="C398">
-        <v>1.00000088208397</v>
+        <v>0.9512229592607641</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -4785,10 +4785,10 @@
         <v>13.16676666666663</v>
       </c>
       <c r="B399">
-        <v>0.937641690178194</v>
+        <v>0.9848909109659812</v>
       </c>
       <c r="C399">
-        <v>1.000001283467877</v>
+        <v>0.9511920842979185</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -4796,10 +4796,10 @@
         <v>13.20009999999996</v>
       </c>
       <c r="B400">
-        <v>0.9376426611297342</v>
+        <v>0.9849590444708506</v>
       </c>
       <c r="C400">
-        <v>1.000001572130843</v>
+        <v>0.9511613905320576</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -4807,10 +4807,10 @@
         <v>13.2334333333333</v>
       </c>
       <c r="B401">
-        <v>0.9376433122584719</v>
+        <v>0.9850236885676877</v>
       </c>
       <c r="C401">
-        <v>1.000001759821231</v>
+        <v>0.9511308301767608</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -4818,10 +4818,10 @@
         <v>13.26676666666663</v>
       </c>
       <c r="B402">
-        <v>0.937645310717459</v>
+        <v>0.9850810614782043</v>
       </c>
       <c r="C402">
-        <v>1.000001736724076</v>
+        <v>0.9511003583432155</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -4829,10 +4829,10 @@
         <v>13.30009999999996</v>
       </c>
       <c r="B403">
-        <v>0.937645957007025</v>
+        <v>0.9851280917847945</v>
       </c>
       <c r="C403">
-        <v>1.000001559553023</v>
+        <v>0.9510699378194983</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -4840,10 +4840,10 @@
         <v>13.3334333333333</v>
       </c>
       <c r="B404">
-        <v>0.9376456841141533</v>
+        <v>0.9851625539152608</v>
       </c>
       <c r="C404">
-        <v>1.000001328914156</v>
+        <v>0.9510395431125582</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -4851,10 +4851,10 @@
         <v>13.36676666666663</v>
       </c>
       <c r="B405">
-        <v>0.9376441770003556</v>
+        <v>0.9851831457303571</v>
       </c>
       <c r="C405">
-        <v>1.000000980842151</v>
+        <v>0.9510091626024626</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -4862,10 +4862,10 @@
         <v>13.40009999999996</v>
       </c>
       <c r="B406">
-        <v>0.9376412859253491</v>
+        <v>0.9851894602034067</v>
       </c>
       <c r="C406">
-        <v>1.000000566228157</v>
+        <v>0.9509787991199435</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -4873,10 +4873,10 @@
         <v>13.4334333333333</v>
       </c>
       <c r="B407">
-        <v>0.9376369967595585</v>
+        <v>0.9851818995831734</v>
       </c>
       <c r="C407">
-        <v>1.00000012864945</v>
+        <v>0.9509484689177494</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -4884,10 +4884,10 @@
         <v>13.46676666666663</v>
       </c>
       <c r="B408">
-        <v>0.9376314299463893</v>
+        <v>0.9851615343028738</v>
       </c>
       <c r="C408">
-        <v>0.9999997088645094</v>
+        <v>0.9509182006383491</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -4895,10 +4895,10 @@
         <v>13.50009999999996</v>
       </c>
       <c r="B409">
-        <v>0.9376248244653695</v>
+        <v>0.9851299512096557</v>
       </c>
       <c r="C409">
-        <v>0.9999993440237972</v>
+        <v>0.9508880323399027</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -4906,10 +4906,10 @@
         <v>13.5334333333333</v>
       </c>
       <c r="B410">
-        <v>0.9376175118766085</v>
+        <v>0.9850891188979715</v>
       </c>
       <c r="C410">
-        <v>0.9999990649036006</v>
+        <v>0.9508580084684466</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -4917,10 +4917,10 @@
         <v>13.56676666666663</v>
       </c>
       <c r="B411">
-        <v>0.937609882876348</v>
+        <v>0.9850412868360248</v>
       </c>
       <c r="C411">
-        <v>0.9999988933912229</v>
+        <v>0.9508281768786275</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -4928,10 +4928,10 @@
         <v>13.60009999999996</v>
       </c>
       <c r="B412">
-        <v>0.9376023496450324</v>
+        <v>0.9849889175744025</v>
       </c>
       <c r="C412">
-        <v>0.9999988408134596</v>
+        <v>0.9507985859896342</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -4939,10 +4939,10 @@
         <v>13.6334333333333</v>
       </c>
       <c r="B413">
-        <v>0.9375953075509799</v>
+        <v>0.9849346325881388</v>
       </c>
       <c r="C413">
-        <v>0.9999989072800798</v>
+        <v>0.9507692816311403</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -4950,10 +4950,10 @@
         <v>13.66676666666663</v>
       </c>
       <c r="B414">
-        <v>0.9375890997083628</v>
+        <v>0.98488116885806</v>
       </c>
       <c r="C414">
-        <v>0.9999990820709399</v>
+        <v>0.9507403052150242</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -4961,10 +4961,10 @@
         <v>13.70009999999996</v>
       </c>
       <c r="B415">
-        <v>0.9375839875159236</v>
+        <v>0.9848312777998918</v>
       </c>
       <c r="C415">
-        <v>0.9999993449949713</v>
+        <v>0.9507116900172886</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -4972,10 +4972,10 @@
         <v>13.73343333333329</v>
       </c>
       <c r="B416">
-        <v>0.9375801296569234</v>
+        <v>0.9847876196370845</v>
       </c>
       <c r="C416">
-        <v>0.9999996685627872</v>
+        <v>0.9506834573271329</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -4983,10 +4983,10 @@
         <v>13.76676666666663</v>
       </c>
       <c r="B417">
-        <v>0.9375775711873114</v>
+        <v>0.9847526180583206</v>
       </c>
       <c r="C417">
-        <v>1.000000020746165</v>
+        <v>0.9506556151371426</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -4994,10 +4994,10 @@
         <v>13.80009999999996</v>
       </c>
       <c r="B418">
-        <v>0.9375762433619947</v>
+        <v>0.9847282902742097</v>
       </c>
       <c r="C418">
-        <v>1.000000368052396</v>
+        <v>0.9506281551104672</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -5005,10 +5005,10 @@
         <v>13.83343333333329</v>
       </c>
       <c r="B419">
-        <v>0.9375759738426483</v>
+        <v>0.9847161292785449</v>
       </c>
       <c r="C419">
-        <v>1.000000678622641</v>
+        <v>0.9506010534462705</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -5016,10 +5016,10 @@
         <v>13.86676666666663</v>
       </c>
       <c r="B420">
-        <v>0.9375765059899962</v>
+        <v>0.9847169837878843</v>
       </c>
       <c r="C420">
-        <v>1.000000925071729</v>
+        <v>0.9505742731862267</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -5027,10 +5027,10 @@
         <v>13.90009999999996</v>
       </c>
       <c r="B421">
-        <v>0.9375775251553139</v>
+        <v>0.9847310046445643</v>
       </c>
       <c r="C421">
-        <v>1.000001086820435</v>
+        <v>0.9505477661836078</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -5038,10 +5038,10 @@
         <v>13.93343333333329</v>
       </c>
       <c r="B422">
-        <v>0.9375786893189589</v>
+        <v>0.9847576355195861</v>
       </c>
       <c r="C422">
-        <v>1.000001151726311</v>
+        <v>0.9505214785204923</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -5049,10 +5049,10 @@
         <v>13.96676666666663</v>
       </c>
       <c r="B423">
-        <v>0.9375796611229513</v>
+        <v>0.9847956255786819</v>
       </c>
       <c r="C423">
-        <v>1.000001116889706</v>
+        <v>0.9504953542143751</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -5060,10 +5060,10 @@
         <v>14.00009999999996</v>
       </c>
       <c r="B424">
-        <v>0.9375801383272807</v>
+        <v>0.9848430904877241</v>
       </c>
       <c r="C424">
-        <v>1.0000009885909</v>
+        <v>0.9504693409857743</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -5071,10 +5071,10 @@
         <v>14.03343333333329</v>
       </c>
       <c r="B425">
-        <v>0.9375798799753012</v>
+        <v>0.9848975642086463</v>
       </c>
       <c r="C425">
-        <v>1.000000781394716</v>
+        <v>0.9504433948575717</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -5082,10 +5082,10 @@
         <v>14.06676666666663</v>
       </c>
       <c r="B426">
-        <v>0.9375787260466137</v>
+        <v>0.9849561007140979</v>
       </c>
       <c r="C426">
-        <v>1.000000516533318</v>
+        <v>0.950417482389744</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -5093,10 +5093,10 @@
         <v>14.10009999999996</v>
       </c>
       <c r="B427">
-        <v>0.9375766090507852</v>
+        <v>0.9850153598190406</v>
       </c>
       <c r="C427">
-        <v>1.000000219739632</v>
+        <v>0.9503915815866072</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -5104,10 +5104,10 @@
         <v>14.13343333333329</v>
       </c>
       <c r="B428">
-        <v>0.9375735568029988</v>
+        <v>0.985071773937218</v>
       </c>
       <c r="C428">
-        <v>0.9999999187477313</v>
+        <v>0.9503656817622335</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -5115,10 +5115,10 @@
         <v>14.16676666666663</v>
       </c>
       <c r="B429">
-        <v>0.9375696864479879</v>
+        <v>0.9851217389540284</v>
       </c>
       <c r="C429">
-        <v>0.9999996406992729</v>
+        <v>0.950339784517306</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -5126,10 +5126,10 @@
         <v>14.20009999999996</v>
       </c>
       <c r="B430">
-        <v>0.9375651905864778</v>
+        <v>0.9851618496638941</v>
       </c>
       <c r="C430">
-        <v>0.9999994096952995</v>
+        <v>0.9503139025909086</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -5137,10 +5137,10 @@
         <v>14.23343333333329</v>
       </c>
       <c r="B431">
-        <v>0.9375603170406854</v>
+        <v>0.985189157322549</v>
       </c>
       <c r="C431">
-        <v>0.999999244711082</v>
+        <v>0.950288058679974</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -5148,10 +5148,10 @@
         <v>14.26676666666663</v>
       </c>
       <c r="B432">
-        <v>0.9375553443159133</v>
+        <v>0.9852014209428671</v>
       </c>
       <c r="C432">
-        <v>0.9999991580510131</v>
+        <v>0.9502622838171643</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -5159,10 +5159,10 @@
         <v>14.30009999999996</v>
       </c>
       <c r="B433">
-        <v>0.9375505551334341</v>
+        <v>0.985197320437731</v>
       </c>
       <c r="C433">
-        <v>0.9999991544651272</v>
+        <v>0.9502366151618301</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -5170,10 +5170,10 @@
         <v>14.33343333333329</v>
       </c>
       <c r="B434">
-        <v>0.9375462105038667</v>
+        <v>0.9851766045641955</v>
       </c>
       <c r="C434">
-        <v>0.9999992309842564</v>
+        <v>0.9502110932035207</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -5181,10 +5181,10 @@
         <v>14.36676666666663</v>
       </c>
       <c r="B435">
-        <v>0.9375425266784098</v>
+        <v>0.985140156935412</v>
       </c>
       <c r="C435">
-        <v>0.9999993774633527</v>
+        <v>0.9501857585473961</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -5192,10 +5192,10 @@
         <v>14.40009999999996</v>
       </c>
       <c r="B436">
-        <v>0.9375396569756851</v>
+        <v>0.9850899761475279</v>
       </c>
       <c r="C436">
-        <v>0.9999995777583833</v>
+        <v>0.9501606486196905</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -5203,10 +5203,10 @@
         <v>14.43343333333329</v>
       </c>
       <c r="B437">
-        <v>0.9375376799712974</v>
+        <v>0.9850290759000088</v>
       </c>
       <c r="C437">
-        <v>0.9999998114071882</v>
+        <v>0.9501357947488067</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -5214,10 +5214,10 @@
         <v>14.46676666666663</v>
       </c>
       <c r="B438">
-        <v>0.9375365949067197</v>
+        <v>0.984961315658995</v>
       </c>
       <c r="C438">
-        <v>1.000000055643461</v>
+        <v>0.9501112200269798</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -5225,10 +5225,10 @@
         <v>14.50009999999996</v>
       </c>
       <c r="B439">
-        <v>0.9375363244853953</v>
+        <v>0.9848911720637877</v>
       </c>
       <c r="C439">
-        <v>1.000000287548829</v>
+        <v>0.950086938196854</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -5236,10 +5236,10 @@
         <v>14.53343333333329</v>
       </c>
       <c r="B440">
-        <v>0.9375367245424997</v>
+        <v>0.9848234588858137</v>
       </c>
       <c r="C440">
-        <v>1.000000486142443</v>
+        <v>0.9500629535776659</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -5247,10 +5247,10 @@
         <v>14.56676666666663</v>
       </c>
       <c r="B441">
-        <v>0.9375375994636773</v>
+        <v>0.9847630029542823</v>
       </c>
       <c r="C441">
-        <v>1.00000063422032</v>
+        <v>0.9500392618290788</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -5258,10 +5258,10 @@
         <v>14.60009999999996</v>
       </c>
       <c r="B442">
-        <v>0.9375387217419959</v>
+        <v>0.9847142879983798</v>
       </c>
       <c r="C442">
-        <v>1.000000719786146</v>
+        <v>0.9500158512194984</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -5269,10 +5269,10 @@
         <v>14.63343333333329</v>
       </c>
       <c r="B443">
-        <v>0.9375398537419042</v>
+        <v>0.9846810879764433</v>
       </c>
       <c r="C443">
-        <v>1.000000736957971</v>
+        <v>0.9499927040578289</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -5280,10 +5280,10 @@
         <v>14.66676666666662</v>
       </c>
       <c r="B444">
-        <v>0.9375407696078463</v>
+        <v>0.9846661231212608</v>
       </c>
       <c r="C444">
-        <v>1.000000686286946</v>
+        <v>0.9499697980566442</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -5291,10 +5291,10 @@
         <v>14.70009999999996</v>
       </c>
       <c r="B445">
-        <v>0.9375412753178576</v>
+        <v>0.9846707807144656</v>
       </c>
       <c r="C445">
-        <v>1.000000574479892</v>
+        <v>0.949947107558842</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -5302,10 +5302,10 @@
         <v>14.73343333333329</v>
       </c>
       <c r="B446">
-        <v>0.9375412251253413</v>
+        <v>0.9846949433049698</v>
       </c>
       <c r="C446">
-        <v>1.000000413571958</v>
+        <v>0.9499246047134422</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -5313,10 +5313,10 @@
         <v>14.76676666666662</v>
       </c>
       <c r="B447">
-        <v>0.9375405330255671</v>
+        <v>0.9847369573606926</v>
       </c>
       <c r="C447">
-        <v>1.000000219643957</v>
+        <v>0.9499022607534137</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -5324,10 +5324,10 @@
         <v>14.80009999999996</v>
       </c>
       <c r="B448">
-        <v>0.9375391783852118</v>
+        <v>0.9847937558592353</v>
       </c>
       <c r="C448">
-        <v>1.000000011217018</v>
+        <v>0.949880047473711</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -5335,10 +5335,10 @@
         <v>14.83343333333329</v>
       </c>
       <c r="B449">
-        <v>0.937537205433821</v>
+        <v>0.9848611236577882</v>
       </c>
       <c r="C449">
-        <v>0.9999998074819217</v>
+        <v>0.9498579388696032</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -5346,10 +5346,10 @@
         <v>14.86676666666662</v>
       </c>
       <c r="B450">
-        <v>0.9375347168825726</v>
+        <v>0.9849340711373679</v>
       </c>
       <c r="C450">
-        <v>0.9999996265299627</v>
+        <v>0.9498359127376614</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -5357,10 +5357,10 @@
         <v>14.90009999999996</v>
       </c>
       <c r="B451">
-        <v>0.9375318624575838</v>
+        <v>0.9850072659786221</v>
       </c>
       <c r="C451">
-        <v>0.9999994837462554</v>
+        <v>0.9498139519519093</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -5368,10 +5368,10 @@
         <v>14.93343333333329</v>
       </c>
       <c r="B452">
-        <v>0.9375288235671707</v>
+        <v>0.9850754689762714</v>
       </c>
       <c r="C452">
-        <v>0.9999993905059177</v>
+        <v>0.9497920451598015</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -5379,10 +5379,10 @@
         <v>14.96676666666662</v>
       </c>
       <c r="B453">
-        <v>0.9375257956297491</v>
+        <v>0.9851339276901729</v>
       </c>
       <c r="C453">
-        <v>0.9999993532810945</v>
+        <v>0.949770186792608</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -5390,10 +5390,10 @@
         <v>15</v>
       </c>
       <c r="B454">
-        <v>0.9375229785196869</v>
+        <v>0.9851785883296522</v>
       </c>
       <c r="C454">
-        <v>0.9999993730602585</v>
+        <v>0.9497484418437252</v>
       </c>
     </row>
   </sheetData>
